--- a/Zinc/7. Sensitivity analyses/Plots of DIC SA/Carbonate_system_SA.xlsx
+++ b/Zinc/7. Sensitivity analyses/Plots of DIC SA/Carbonate_system_SA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ornl-my.sharepoint.com/personal/q4q_ornl_gov/Documents/Research/Bioavailability Project/BLM_spatial_assessmt/Zinc/7. Sensitivity analyses/Plots of DIC SA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="11_1521FF94F78433F6D3971F452C382FE477721A72" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E7F7180-3AA9-4DC0-9794-1D1E2DE758D7}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_27F50F9DD8F835CF593FF6452A392FE477740235" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA220FE6-512E-4D25-9E70-4B70BFA5999D}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="19200" windowHeight="11280" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Delta" sheetId="1" r:id="rId1"/>
@@ -18,10 +18,6 @@
     <sheet name="Log Response Ratio" sheetId="3" r:id="rId3"/>
     <sheet name="Robustness" sheetId="4" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Log Response Ratio'!$A$1:$H$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Percent Change'!$A$1:$H$1</definedName>
-  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -209,10 +205,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -531,22 +523,22 @@
         <v>-15.381072415721</v>
       </c>
       <c r="C2">
-        <v>1.1074039463210601</v>
+        <v>1.11777365141558</v>
       </c>
       <c r="D2">
-        <v>4.0884580165822504</v>
+        <v>4.2738697025867998</v>
       </c>
       <c r="E2">
-        <v>7.1929165173225096</v>
+        <v>7.65577750611466</v>
       </c>
       <c r="F2">
-        <v>9.4508774139967002</v>
+        <v>10.4756976426756</v>
       </c>
       <c r="G2">
-        <v>73.353589868929006</v>
+        <v>80.496988630329696</v>
       </c>
       <c r="H2">
-        <v>8.3434734676756399</v>
+        <v>9.3579239912600496</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -557,22 +549,22 @@
         <v>-5.4929940596082396</v>
       </c>
       <c r="C3">
-        <v>2.7007941022505099E-2</v>
+        <v>2.5795306862752901E-2</v>
       </c>
       <c r="D3">
-        <v>7.9080700321476502E-2</v>
+        <v>7.7088026934069506E-2</v>
       </c>
       <c r="E3">
-        <v>4.47387392578329E-2</v>
+        <v>4.6524934654724598E-2</v>
       </c>
       <c r="F3">
-        <v>0.16557790902260799</v>
+        <v>0.15555863194793901</v>
       </c>
       <c r="G3">
         <v>0.83585205423731002</v>
       </c>
       <c r="H3">
-        <v>0.13856996800010299</v>
+        <v>0.12976332508518601</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -583,22 +575,22 @@
         <v>-85.704300545331094</v>
       </c>
       <c r="C4">
-        <v>4.2416157391977896E-3</v>
+        <v>3.1619005374031498E-3</v>
       </c>
       <c r="D4">
-        <v>1.7008386019035201E-2</v>
+        <v>1.38660610771168E-2</v>
       </c>
       <c r="E4">
-        <v>-0.61240943526370295</v>
+        <v>-0.56435077171494996</v>
       </c>
       <c r="F4">
-        <v>4.51781476812348E-2</v>
+        <v>4.0703850012757399E-2</v>
       </c>
       <c r="G4">
         <v>1.0109513226553</v>
       </c>
       <c r="H4">
-        <v>4.0936531942037002E-2</v>
+        <v>3.7541949475354199E-2</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -609,22 +601,22 @@
         <v>-15.802621433636</v>
       </c>
       <c r="C5">
-        <v>-3.3969554391610801</v>
+        <v>-3.3359544016065201</v>
       </c>
       <c r="D5">
-        <v>-1.8958711128780401</v>
+        <v>-1.83906102846354</v>
       </c>
       <c r="E5">
-        <v>-0.63835822684856403</v>
+        <v>-0.68323727767007703</v>
       </c>
       <c r="F5">
-        <v>-0.89157575940135503</v>
+        <v>-0.81159449646928095</v>
       </c>
       <c r="G5">
         <v>130.89374917285599</v>
       </c>
       <c r="H5">
-        <v>2.5053796797597201</v>
+        <v>2.5243599051372398</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -635,22 +627,22 @@
         <v>-109.229246092468</v>
       </c>
       <c r="C6">
-        <v>-20.418285950896198</v>
+        <v>-21.797856519789701</v>
       </c>
       <c r="D6">
-        <v>-13.567458490015801</v>
+        <v>-13.801536802304801</v>
       </c>
       <c r="E6">
-        <v>-14.5292887360146</v>
+        <v>-15.215318678641299</v>
       </c>
       <c r="F6">
-        <v>-4.7653179180429204</v>
+        <v>-4.8152545284452302</v>
       </c>
       <c r="G6">
         <v>29.174913152019201</v>
       </c>
       <c r="H6">
-        <v>15.652968032853201</v>
+        <v>16.982601991344399</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -661,22 +653,22 @@
         <v>-0.57125093544385397</v>
       </c>
       <c r="C7">
-        <v>1.6652630663305301E-2</v>
+        <v>1.68285281543228E-2</v>
       </c>
       <c r="D7">
-        <v>5.2726691068816299E-2</v>
+        <v>5.3050591697356202E-2</v>
       </c>
       <c r="E7">
-        <v>7.0672674183698603E-2</v>
+        <v>7.3585170515330506E-2</v>
       </c>
       <c r="F7">
-        <v>0.109034264256236</v>
+        <v>0.11136628425001401</v>
       </c>
       <c r="G7">
         <v>0.69407146696676003</v>
       </c>
       <c r="H7">
-        <v>9.2381633592931195E-2</v>
+        <v>9.4537756095691206E-2</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -687,22 +679,22 @@
         <v>-2.3132318976992802E-2</v>
       </c>
       <c r="C8">
-        <v>4.1076435872492302E-4</v>
+        <v>4.0348903688688698E-4</v>
       </c>
       <c r="D8">
-        <v>2.1785880391367199E-3</v>
+        <v>2.1919844411799698E-3</v>
       </c>
       <c r="E8">
-        <v>4.3858688522135101E-3</v>
+        <v>5.11329108540233E-3</v>
       </c>
       <c r="F8">
-        <v>5.8613542621919201E-3</v>
+        <v>6.1840372232724299E-3</v>
       </c>
       <c r="G8">
         <v>0.158968435637341</v>
       </c>
       <c r="H8">
-        <v>5.4505899034669996E-3</v>
+        <v>5.7805481863855398E-3</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
@@ -719,16 +711,16 @@
         <v>8.8012017179612601E-13</v>
       </c>
       <c r="E9">
-        <v>2.7363506429837601E-12</v>
+        <v>3.5525907240701302E-12</v>
       </c>
       <c r="F9">
-        <v>2.6337430704085399E-12</v>
+        <v>3.0771118786972601E-12</v>
       </c>
       <c r="G9">
         <v>8.6595883967004301E-11</v>
       </c>
       <c r="H9">
-        <v>2.6337430704085399E-12</v>
+        <v>3.0771118786972601E-12</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -739,22 +731,22 @@
         <v>-97.581557759256995</v>
       </c>
       <c r="C10">
-        <v>3.8747027319397702</v>
+        <v>3.8918220209588998</v>
       </c>
       <c r="D10">
-        <v>8.3807009873634009</v>
+        <v>8.5144053293994002</v>
       </c>
       <c r="E10">
-        <v>8.4670168907194903</v>
+        <v>8.6817506098497805</v>
       </c>
       <c r="F10">
-        <v>13.4438613336049</v>
+        <v>13.5557802667731</v>
       </c>
       <c r="G10">
         <v>51.366511162332003</v>
       </c>
       <c r="H10">
-        <v>9.5691586016650998</v>
+        <v>9.6639582458142002</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -765,22 +757,22 @@
         <v>-4227182.2167094797</v>
       </c>
       <c r="C11">
-        <v>-2473094.9699005601</v>
+        <v>-2493166.6121119601</v>
       </c>
       <c r="D11">
-        <v>-1833514.8197365899</v>
+        <v>-1872790.01693242</v>
       </c>
       <c r="E11">
-        <v>-1473709.80053903</v>
+        <v>-1518543.09884923</v>
       </c>
       <c r="F11">
-        <v>-1124767.6302445999</v>
+        <v>-1128984.8298474699</v>
       </c>
       <c r="G11">
         <v>24233975.680544998</v>
       </c>
       <c r="H11">
-        <v>1348327.33965596</v>
+        <v>1364181.7822644899</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -788,25 +780,25 @@
         <v>18</v>
       </c>
       <c r="B12">
-        <v>-1207203.67522153</v>
+        <v>-1313014.6980984099</v>
       </c>
       <c r="C12">
-        <v>-172907.286469126</v>
+        <v>-197739.08570641599</v>
       </c>
       <c r="D12">
-        <v>-91990.834334865096</v>
+        <v>-95842.000519041801</v>
       </c>
       <c r="E12">
-        <v>-139712.49602734001</v>
+        <v>-164673.49499102501</v>
       </c>
       <c r="F12">
-        <v>-40741.544125921799</v>
+        <v>-42478.146042412904</v>
       </c>
       <c r="G12">
         <v>24084.828737613901</v>
       </c>
       <c r="H12">
-        <v>132165.74234320401</v>
+        <v>155260.939664003</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
@@ -817,22 +809,22 @@
         <v>-7.0924223479097997E-11</v>
       </c>
       <c r="C13">
-        <v>-2.6285707176725902E-12</v>
+        <v>-2.7977997843896599E-12</v>
       </c>
       <c r="D13">
-        <v>-1.30761341311364E-12</v>
+        <v>-1.41658355360436E-12</v>
       </c>
       <c r="E13">
-        <v>-2.2937618430150599E-12</v>
+        <v>-2.5880822096539002E-12</v>
       </c>
       <c r="F13">
-        <v>-5.5242149522427601E-13</v>
+        <v>-5.7013565084091204E-13</v>
       </c>
       <c r="G13">
         <v>1.1516559403175901E-12</v>
       </c>
       <c r="H13">
-        <v>2.0761492224483099E-12</v>
+        <v>2.2276641335487402E-12</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
@@ -840,25 +832,25 @@
         <v>20</v>
       </c>
       <c r="B14">
-        <v>-5.1710297727306197E-11</v>
+        <v>-6.6761954034308002E-11</v>
       </c>
       <c r="C14">
-        <v>-8.7386461837398998E-13</v>
+        <v>-1.0559887209922E-12</v>
       </c>
       <c r="D14">
-        <v>-2.3889290625151599E-13</v>
+        <v>-2.6513259090437801E-13</v>
       </c>
       <c r="E14">
-        <v>-1.1805554915130401E-12</v>
+        <v>-1.72018490808414E-12</v>
       </c>
       <c r="F14">
-        <v>-7.0187592688376705E-14</v>
+        <v>-7.2553847237906501E-14</v>
       </c>
       <c r="G14">
         <v>6.1117661275200306E-14</v>
       </c>
       <c r="H14">
-        <v>8.0367702568561304E-13</v>
+        <v>9.8343487375429303E-13</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
@@ -869,22 +861,22 @@
         <v>-24138.003254847699</v>
       </c>
       <c r="C15">
-        <v>-9461.2999674836901</v>
+        <v>-9599.1464377221</v>
       </c>
       <c r="D15">
-        <v>-6315.8180410027999</v>
+        <v>-6358.7606149439998</v>
       </c>
       <c r="E15">
-        <v>-6102.8868618402403</v>
+        <v>-6179.6649983507996</v>
       </c>
       <c r="F15">
-        <v>-3004.0287981592001</v>
+        <v>-3015.12088185519</v>
       </c>
       <c r="G15">
         <v>42080.290768353698</v>
       </c>
       <c r="H15">
-        <v>6457.2711693244901</v>
+        <v>6584.0255558669096</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
@@ -895,22 +887,22 @@
         <v>-3282.23450196674</v>
       </c>
       <c r="C16">
-        <v>-1229.59306736447</v>
+        <v>-1196.01887149657</v>
       </c>
       <c r="D16">
-        <v>-705.96259860167197</v>
+        <v>-648.93179008151901</v>
       </c>
       <c r="E16">
-        <v>1268.56071980857</v>
+        <v>1151.9033724533199</v>
       </c>
       <c r="F16">
-        <v>-264.08772546559999</v>
+        <v>-221.536945455015</v>
       </c>
       <c r="G16">
         <v>209925.550734624</v>
       </c>
       <c r="H16">
-        <v>965.50534189887298</v>
+        <v>974.48192604155497</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
@@ -921,22 +913,22 @@
         <v>-9608.2221716641998</v>
       </c>
       <c r="C17">
-        <v>75.853961334362495</v>
+        <v>74.968653507312197</v>
       </c>
       <c r="D17">
-        <v>175.16231309855499</v>
+        <v>168.75264918780999</v>
       </c>
       <c r="E17">
-        <v>125.69766403766</v>
+        <v>126.507173616408</v>
       </c>
       <c r="F17">
-        <v>299.28207823104498</v>
+        <v>292.13708785391498</v>
       </c>
       <c r="G17">
         <v>1286.1855793744</v>
       </c>
       <c r="H17">
-        <v>223.42811689668301</v>
+        <v>217.16843434660299</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
@@ -944,25 +936,25 @@
         <v>24</v>
       </c>
       <c r="B18">
-        <v>-60168.910749780502</v>
+        <v>-61146.130747147297</v>
       </c>
       <c r="C18">
-        <v>-26197.183615295198</v>
+        <v>-26799.899160323501</v>
       </c>
       <c r="D18">
-        <v>-17242.251942661798</v>
+        <v>-17873.041542770799</v>
       </c>
       <c r="E18">
-        <v>-16474.011703608499</v>
+        <v>-17069.210758665198</v>
       </c>
       <c r="F18">
-        <v>-7198.1171458901399</v>
+        <v>-7206.6096095113598</v>
       </c>
       <c r="G18">
         <v>82096.386904595594</v>
       </c>
       <c r="H18">
-        <v>18999.066469405101</v>
+        <v>19593.289550812198</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
@@ -973,22 +965,22 @@
         <v>-18969.074517372101</v>
       </c>
       <c r="C19">
-        <v>-5554.18162662136</v>
+        <v>-5278.5422681722603</v>
       </c>
       <c r="D19">
-        <v>-3154.2906810955201</v>
+        <v>-2782.7875612729299</v>
       </c>
       <c r="E19">
-        <v>2975.4315281240802</v>
+        <v>2641.14583495855</v>
       </c>
       <c r="F19">
-        <v>-1174.60863879871</v>
+        <v>-1088.5331889198901</v>
       </c>
       <c r="G19">
         <v>607018.25714204495</v>
       </c>
       <c r="H19">
-        <v>4379.5729878226502</v>
+        <v>4190.0090792523797</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
@@ -999,22 +991,22 @@
         <v>-26551.966584520502</v>
       </c>
       <c r="C20">
-        <v>195.742700270798</v>
+        <v>197.26439859368699</v>
       </c>
       <c r="D20">
-        <v>446.10305849346003</v>
+        <v>432.55658965787597</v>
       </c>
       <c r="E20">
-        <v>374.58102890126099</v>
+        <v>385.51666220896902</v>
       </c>
       <c r="F20">
-        <v>964.75787358937396</v>
+        <v>932.72888079805</v>
       </c>
       <c r="G20">
         <v>2700.06785285659</v>
       </c>
       <c r="H20">
-        <v>769.01517331857599</v>
+        <v>735.46448220436298</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
@@ -1025,22 +1017,22 @@
         <v>-3776.70229329517</v>
       </c>
       <c r="C21">
-        <v>-230.70420706802801</v>
+        <v>-281.15042353802602</v>
       </c>
       <c r="D21">
-        <v>-105.598753436724</v>
+        <v>-123.178033062236</v>
       </c>
       <c r="E21">
-        <v>-208.37793838084801</v>
+        <v>-253.078788828087</v>
       </c>
       <c r="F21">
-        <v>-44.2765467823153</v>
+        <v>-47.444685546016899</v>
       </c>
       <c r="G21">
         <v>1206.8243863370899</v>
       </c>
       <c r="H21">
-        <v>186.42766028571199</v>
+        <v>233.70573799200901</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
@@ -1051,22 +1043,22 @@
         <v>-494.94423254304002</v>
       </c>
       <c r="C22">
-        <v>-44.899265139219999</v>
+        <v>-47.181365007653802</v>
       </c>
       <c r="D22">
-        <v>-20.619313811914701</v>
+        <v>-22.112455736255001</v>
       </c>
       <c r="E22">
-        <v>-33.481004067161102</v>
+        <v>-36.220256376076499</v>
       </c>
       <c r="F22">
-        <v>-9.6107246189170592</v>
+        <v>-10.01857289837</v>
       </c>
       <c r="G22">
         <v>203.229325312903</v>
       </c>
       <c r="H22">
-        <v>35.288540520302902</v>
+        <v>37.162792109283799</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
@@ -1077,22 +1069,22 @@
         <v>-102.26480429140101</v>
       </c>
       <c r="C23">
-        <v>-19.148788658890101</v>
+        <v>-19.571911875900099</v>
       </c>
       <c r="D23">
         <v>-10.2467260188991</v>
       </c>
       <c r="E23">
-        <v>-9.0133478403538092</v>
+        <v>-9.6958137171118608</v>
       </c>
       <c r="F23">
-        <v>-5.52262515536765</v>
+        <v>-5.6858759229122597</v>
       </c>
       <c r="G23">
         <v>500.90705827621002</v>
       </c>
       <c r="H23">
-        <v>13.6261635035225</v>
+        <v>13.8860359529879</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
@@ -1103,22 +1095,22 @@
         <v>-270.77112463309999</v>
       </c>
       <c r="C24">
-        <v>8.7756246713866002</v>
+        <v>8.9439531336665308</v>
       </c>
       <c r="D24">
-        <v>21.461772803377499</v>
+        <v>23.0282282132065</v>
       </c>
       <c r="E24">
-        <v>37.285403099577799</v>
+        <v>41.400817677973897</v>
       </c>
       <c r="F24">
-        <v>49.0362879190792</v>
+        <v>55.376318641719799</v>
       </c>
       <c r="G24">
-        <v>388.56569517520001</v>
+        <v>880.74193627110105</v>
       </c>
       <c r="H24">
-        <v>40.260663247692598</v>
+        <v>46.432365508053302</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
@@ -1126,25 +1118,25 @@
         <v>31</v>
       </c>
       <c r="B25">
-        <v>-243.88100428039999</v>
+        <v>-249.336949309505</v>
       </c>
       <c r="C25">
-        <v>1.48084788875732</v>
+        <v>1.55359902720419</v>
       </c>
       <c r="D25">
-        <v>3.7202525504653501</v>
+        <v>3.7943337360957501</v>
       </c>
       <c r="E25">
-        <v>7.3544609378752801</v>
+        <v>8.18113633257685</v>
       </c>
       <c r="F25">
-        <v>10.566683528168101</v>
+        <v>10.8554871758317</v>
       </c>
       <c r="G25">
-        <v>174.24849829695</v>
+        <v>201.74297787889</v>
       </c>
       <c r="H25">
-        <v>9.0858356394107496</v>
+        <v>9.3018881486275493</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
@@ -1155,22 +1147,22 @@
         <v>-1.66156316777285E-4</v>
       </c>
       <c r="C26">
-        <v>1.48130028443935E-5</v>
+        <v>1.48828201106729E-5</v>
       </c>
       <c r="D26">
-        <v>4.9342230092212003E-5</v>
+        <v>5.0759174528211002E-5</v>
       </c>
       <c r="E26">
-        <v>9.1236312263022506E-5</v>
+        <v>9.4630754540868202E-5</v>
       </c>
       <c r="F26">
-        <v>1.16417203791951E-4</v>
+        <v>1.21797996049185E-4</v>
       </c>
       <c r="G26">
         <v>9.2757985648147005E-4</v>
       </c>
       <c r="H26">
-        <v>1.01604200947557E-4</v>
+        <v>1.06915175938513E-4</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
@@ -1181,22 +1173,22 @@
         <v>-0.10902772888114701</v>
       </c>
       <c r="C27">
-        <v>1.6530304982760001E-3</v>
+        <v>1.68027332012449E-3</v>
       </c>
       <c r="D27">
-        <v>2.3055617546529602E-3</v>
+        <v>2.3320626322799998E-3</v>
       </c>
       <c r="E27">
-        <v>1.17542274184975E-3</v>
+        <v>1.2525355663362599E-3</v>
       </c>
       <c r="F27">
-        <v>2.67316950659274E-3</v>
+        <v>2.6897538416945101E-3</v>
       </c>
       <c r="G27">
         <v>3.7610096893310198E-3</v>
       </c>
       <c r="H27">
-        <v>1.0201390083167401E-3</v>
+        <v>1.0094805215700199E-3</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
@@ -1207,22 +1199,22 @@
         <v>-1.7941493697866001E-3</v>
       </c>
       <c r="C28">
-        <v>-2.6339583930784998E-4</v>
+        <v>-2.9084871528647297E-4</v>
       </c>
       <c r="D28">
-        <v>-1.2296699812747001E-4</v>
+        <v>-1.3740523228799499E-4</v>
       </c>
       <c r="E28">
-        <v>-1.8718855039271399E-4</v>
+        <v>-2.09181248637458E-4</v>
       </c>
       <c r="F28">
-        <v>-6.4127783426345001E-5</v>
+        <v>-6.9365472359352395E-5</v>
       </c>
       <c r="G28">
         <v>1.2524722804679899E-4</v>
       </c>
       <c r="H28">
-        <v>1.9926805588150499E-4</v>
+        <v>2.2148324292712101E-4</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
@@ -1233,22 +1225,22 @@
         <v>-5.9582971146589997E-3</v>
       </c>
       <c r="C29">
-        <v>1.191779108973E-4</v>
+        <v>1.1985228712230001E-4</v>
       </c>
       <c r="D29">
-        <v>1.8896549080720299E-4</v>
+        <v>1.8918221547869999E-4</v>
       </c>
       <c r="E29">
-        <v>1.8274002189702001E-4</v>
+        <v>1.8461677229112699E-4</v>
       </c>
       <c r="F29">
-        <v>2.7724730026719798E-4</v>
+        <v>2.8165491810632799E-4</v>
       </c>
       <c r="G29">
         <v>8.0481365346869705E-4</v>
       </c>
       <c r="H29">
-        <v>1.58069389369898E-4</v>
+        <v>1.61802630984028E-4</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
@@ -1256,25 +1248,25 @@
         <v>36</v>
       </c>
       <c r="B30">
-        <v>-7.6838368007390103E-4</v>
+        <v>-9.6695681519960003E-4</v>
       </c>
       <c r="C30">
-        <v>-2.37188667747782E-4</v>
+        <v>-2.35672267313049E-4</v>
       </c>
       <c r="D30">
-        <v>-1.4240422956378999E-4</v>
+        <v>-1.40690270800074E-4</v>
       </c>
       <c r="E30">
-        <v>3.7987873502567398E-5</v>
+        <v>1.9695437796516799E-5</v>
       </c>
       <c r="F30">
-        <v>-6.4247557094385105E-5</v>
+        <v>-6.4800827059847504E-5</v>
       </c>
       <c r="G30">
         <v>2.42187366642834E-2</v>
       </c>
       <c r="H30">
-        <v>1.72941110653397E-4</v>
+        <v>1.7087144025320199E-4</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
@@ -1285,22 +1277,22 @@
         <v>-1.6630544948169101E-3</v>
       </c>
       <c r="C31">
-        <v>1.35182660603646E-5</v>
+        <v>1.25750804166047E-5</v>
       </c>
       <c r="D31">
-        <v>3.4339734869150399E-5</v>
+        <v>3.2041883374801802E-5</v>
       </c>
       <c r="E31">
-        <v>2.6697958113284002E-5</v>
+        <v>2.66182853147252E-5</v>
       </c>
       <c r="F31">
-        <v>6.5392172527569501E-5</v>
+        <v>6.3173473067235206E-5</v>
       </c>
       <c r="G31">
         <v>2.9198909318277003E-4</v>
       </c>
       <c r="H31">
-        <v>5.1873906467204903E-5</v>
+        <v>5.0598392650630501E-5</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
@@ -1311,22 +1303,22 @@
         <v>-1.7456829613396901E-3</v>
       </c>
       <c r="C32">
-        <v>3.3421961147595497E-5</v>
+        <v>3.3807746962220799E-5</v>
       </c>
       <c r="D32">
-        <v>8.6686892467750204E-5</v>
+        <v>8.8386555109915503E-5</v>
       </c>
       <c r="E32">
-        <v>1.17934270376307E-4</v>
+        <v>1.2124903985559301E-4</v>
       </c>
       <c r="F32">
-        <v>1.77135509937369E-4</v>
+        <v>1.83589075055596E-4</v>
       </c>
       <c r="G32">
-        <v>9.9656857143405803E-4</v>
+        <v>1.06311078835187E-3</v>
       </c>
       <c r="H32">
-        <v>1.43713548789773E-4</v>
+        <v>1.4978132809337501E-4</v>
       </c>
     </row>
   </sheetData>
@@ -1371,262 +1363,262 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="B2">
-        <v>-10.902772888114701</v>
+        <v>-1538.1072415721001</v>
       </c>
       <c r="C2">
-        <v>0.1653030498276</v>
-      </c>
-      <c r="D2" s="1">
-        <v>0.230556175465296</v>
+        <v>111.77736514155799</v>
+      </c>
+      <c r="D2">
+        <v>427.38697025867998</v>
       </c>
       <c r="E2">
-        <v>0.117542274184975</v>
+        <v>765.57775061146594</v>
       </c>
       <c r="F2">
-        <v>0.26731695065927402</v>
+        <v>1047.56976426756</v>
       </c>
       <c r="G2">
-        <v>0.37610096893310202</v>
-      </c>
-      <c r="H2" s="1">
-        <v>0.102013900831674</v>
+        <v>8049.6988630329697</v>
+      </c>
+      <c r="H2">
+        <v>935.79239912600497</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="B3">
-        <v>-0.17941493697866001</v>
+        <v>-549.29940596082395</v>
       </c>
       <c r="C3">
-        <v>-2.6339583930785001E-2</v>
-      </c>
-      <c r="D3" s="1">
-        <v>-1.2296699812746999E-2</v>
+        <v>2.57953068627529</v>
+      </c>
+      <c r="D3">
+        <v>7.70880269340695</v>
       </c>
       <c r="E3">
-        <v>-1.8718855039271402E-2</v>
+        <v>4.6524934654724603</v>
       </c>
       <c r="F3">
-        <v>-6.4127783426344998E-3</v>
+        <v>15.555863194793901</v>
       </c>
       <c r="G3">
-        <v>1.2524722804679899E-2</v>
-      </c>
-      <c r="H3" s="1">
-        <v>1.9926805588150499E-2</v>
+        <v>83.585205423730997</v>
+      </c>
+      <c r="H3">
+        <v>12.976332508518601</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="B4">
-        <v>-0.59582971146590002</v>
+        <v>-8570.4300545331098</v>
       </c>
       <c r="C4">
-        <v>1.191779108973E-2</v>
-      </c>
-      <c r="D4" s="1">
-        <v>1.8896549080720301E-2</v>
+        <v>0.316190053740315</v>
+      </c>
+      <c r="D4">
+        <v>1.38660610771168</v>
       </c>
       <c r="E4">
-        <v>1.8274002189702002E-2</v>
+        <v>-56.435077171495003</v>
       </c>
       <c r="F4">
-        <v>2.7724730026719799E-2</v>
+        <v>4.0703850012757297</v>
       </c>
       <c r="G4">
-        <v>8.0481365346869699E-2</v>
-      </c>
-      <c r="H4" s="1">
-        <v>1.5806938936989801E-2</v>
+        <v>101.09513226553</v>
+      </c>
+      <c r="H4">
+        <v>3.7541949475354199</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="B5">
-        <v>-7.6838368007390107E-2</v>
+        <v>-1580.2621433636</v>
       </c>
       <c r="C5">
-        <v>-2.3718866774778202E-2</v>
-      </c>
-      <c r="D5" s="1">
-        <v>-1.4240422956378999E-2</v>
+        <v>-333.595440160652</v>
+      </c>
+      <c r="D5">
+        <v>-183.906102846354</v>
       </c>
       <c r="E5">
-        <v>3.7987873502567399E-3</v>
+        <v>-68.323727767007696</v>
       </c>
       <c r="F5">
-        <v>-6.4247557094385104E-3</v>
+        <v>-81.159449646928095</v>
       </c>
       <c r="G5">
-        <v>2.4218736664283398</v>
-      </c>
-      <c r="H5" s="1">
-        <v>1.72941110653397E-2</v>
+        <v>13089.374917285601</v>
+      </c>
+      <c r="H5">
+        <v>252.43599051372399</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B6">
-        <v>-1.6615631677728501E-2</v>
+        <v>-10922.9246092468</v>
       </c>
       <c r="C6">
-        <v>1.48130028443935E-3</v>
-      </c>
-      <c r="D6" s="1">
-        <v>4.9342230092211999E-3</v>
+        <v>-2179.7856519789598</v>
+      </c>
+      <c r="D6">
+        <v>-1380.1536802304799</v>
       </c>
       <c r="E6">
-        <v>9.1236312263022496E-3</v>
+        <v>-1521.5318678641299</v>
       </c>
       <c r="F6">
-        <v>1.16417203791951E-2</v>
+        <v>-481.52545284452299</v>
       </c>
       <c r="G6">
-        <v>9.2757985648146996E-2</v>
-      </c>
-      <c r="H6" s="1">
-        <v>1.01604200947557E-2</v>
+        <v>2917.4913152019199</v>
+      </c>
+      <c r="H6">
+        <v>1698.26019913444</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="B7">
-        <v>-0.16630544948169099</v>
+        <v>-57.1250935443854</v>
       </c>
       <c r="C7">
-        <v>1.3518266060364599E-3</v>
-      </c>
-      <c r="D7" s="1">
-        <v>3.4339734869150399E-3</v>
+        <v>1.6828528154322799</v>
+      </c>
+      <c r="D7">
+        <v>5.3050591697356202</v>
       </c>
       <c r="E7">
-        <v>2.6697958113283998E-3</v>
+        <v>7.3585170515330498</v>
       </c>
       <c r="F7">
-        <v>6.5392172527569499E-3</v>
+        <v>11.136628425001399</v>
       </c>
       <c r="G7">
-        <v>2.9198909318277001E-2</v>
-      </c>
-      <c r="H7" s="1">
-        <v>5.1873906467204897E-3</v>
+        <v>69.407146696675994</v>
+      </c>
+      <c r="H7">
+        <v>9.4537756095691208</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B8">
-        <v>-1896907.4517372099</v>
+        <v>-2.3132318976992798</v>
       </c>
       <c r="C8">
-        <v>-555418.16266213602</v>
-      </c>
-      <c r="D8" s="1">
-        <v>-315429.06810955203</v>
+        <v>4.0348903688688702E-2</v>
+      </c>
+      <c r="D8">
+        <v>0.21919844411799699</v>
       </c>
       <c r="E8">
-        <v>297543.15281240799</v>
+        <v>0.51132910854023295</v>
       </c>
       <c r="F8">
-        <v>-117460.863879871</v>
+        <v>0.61840372232724194</v>
       </c>
       <c r="G8">
-        <v>60701825.714204498</v>
-      </c>
-      <c r="H8" s="1">
-        <v>437957.29878226598</v>
+        <v>15.8968435637341</v>
+      </c>
+      <c r="H8">
+        <v>0.57805481863855401</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B9">
-        <v>-6016891.0749780498</v>
+        <v>-2.6337430704085401E-10</v>
       </c>
       <c r="C9">
-        <v>-2619718.3615295198</v>
-      </c>
-      <c r="D9" s="1">
-        <v>-1724225.19426618</v>
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>8.8012017179612599E-11</v>
       </c>
       <c r="E9">
-        <v>-1647401.1703608499</v>
+        <v>3.5525907240701298E-10</v>
       </c>
       <c r="F9">
-        <v>-719811.71458901395</v>
+        <v>3.0771118786972598E-10</v>
       </c>
       <c r="G9">
-        <v>8209638.6904595597</v>
-      </c>
-      <c r="H9" s="1">
-        <v>1899906.64694051</v>
+        <v>8.6595883967004301E-9</v>
+      </c>
+      <c r="H9">
+        <v>3.0771118786972598E-10</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="B10">
-        <v>-2655196.6584520498</v>
+        <v>-9758.1557759256993</v>
       </c>
       <c r="C10">
-        <v>19574.270027079801</v>
-      </c>
-      <c r="D10" s="1">
-        <v>44610.305849345998</v>
+        <v>389.18220209588998</v>
+      </c>
+      <c r="D10">
+        <v>851.44053293994</v>
       </c>
       <c r="E10">
-        <v>37458.102890126102</v>
+        <v>868.17506098497802</v>
       </c>
       <c r="F10">
-        <v>96475.787358937407</v>
+        <v>1355.5780266773099</v>
       </c>
       <c r="G10">
-        <v>270006.78528565902</v>
-      </c>
-      <c r="H10" s="1">
-        <v>76901.517331857598</v>
+        <v>5136.6511162331999</v>
+      </c>
+      <c r="H10">
+        <v>966.39582458142002</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B11">
-        <v>-1538.1072415721001</v>
+        <v>-422718221.67094803</v>
       </c>
       <c r="C11">
-        <v>110.740394632106</v>
-      </c>
-      <c r="D11" s="1">
-        <v>408.84580165822501</v>
+        <v>-249316661.21119601</v>
+      </c>
+      <c r="D11">
+        <v>-187279001.69324201</v>
       </c>
       <c r="E11">
-        <v>719.29165173225101</v>
+        <v>-151854309.88492301</v>
       </c>
       <c r="F11">
-        <v>945.08774139966999</v>
+        <v>-112898482.98474699</v>
       </c>
       <c r="G11">
-        <v>7335.3589868929002</v>
-      </c>
-      <c r="H11" s="1">
-        <v>834.34734676756398</v>
+        <v>2423397568.0545001</v>
+      </c>
+      <c r="H11">
+        <v>136418178.22644901</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -1634,103 +1626,103 @@
         <v>18</v>
       </c>
       <c r="B12">
-        <v>-120720367.52215301</v>
+        <v>-131301469.80984101</v>
       </c>
       <c r="C12">
-        <v>-17290728.646912601</v>
-      </c>
-      <c r="D12" s="1">
-        <v>-9199083.4334865101</v>
+        <v>-19773908.5706416</v>
+      </c>
+      <c r="D12">
+        <v>-9584200.0519041903</v>
       </c>
       <c r="E12">
-        <v>-13971249.602733999</v>
+        <v>-16467349.499102499</v>
       </c>
       <c r="F12">
-        <v>-4074154.4125921801</v>
+        <v>-4247814.6042412901</v>
       </c>
       <c r="G12">
         <v>2408482.8737613899</v>
       </c>
-      <c r="H12" s="1">
-        <v>13216574.2343204</v>
+      <c r="H12">
+        <v>15526093.966400299</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13">
-        <v>-5.1710297727306197E-9</v>
+        <v>-7.0924223479098003E-9</v>
       </c>
       <c r="C13">
-        <v>-8.7386461837398995E-11</v>
-      </c>
-      <c r="D13" s="1">
-        <v>-2.3889290625151601E-11</v>
+        <v>-2.79779978438966E-10</v>
+      </c>
+      <c r="D13">
+        <v>-1.4165835536043601E-10</v>
       </c>
       <c r="E13">
-        <v>-1.1805554915130399E-10</v>
+        <v>-2.5880822096539002E-10</v>
       </c>
       <c r="F13">
-        <v>-7.0187592688376699E-12</v>
+        <v>-5.7013565084091202E-11</v>
       </c>
       <c r="G13">
-        <v>6.1117661275200297E-12</v>
-      </c>
-      <c r="H13" s="1">
-        <v>8.0367702568561296E-11</v>
+        <v>1.15165594031759E-10</v>
+      </c>
+      <c r="H13">
+        <v>2.2276641335487399E-10</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B14">
-        <v>-422718221.67094803</v>
+        <v>-6.6761954034308002E-9</v>
       </c>
       <c r="C14">
-        <v>-247309496.99005601</v>
-      </c>
-      <c r="D14" s="1">
-        <v>-183351481.97365901</v>
+        <v>-1.0559887209922E-10</v>
+      </c>
+      <c r="D14">
+        <v>-2.65132590904378E-11</v>
       </c>
       <c r="E14">
-        <v>-147370980.05390301</v>
+        <v>-1.7201849080841399E-10</v>
       </c>
       <c r="F14">
-        <v>-112476763.02446</v>
+        <v>-7.2553847237906499E-12</v>
       </c>
       <c r="G14">
-        <v>2423397568.0545001</v>
-      </c>
-      <c r="H14" s="1">
-        <v>134832733.96559599</v>
+        <v>6.1117661275200297E-12</v>
+      </c>
+      <c r="H14">
+        <v>9.8343487375429295E-11</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B15">
-        <v>-7.0924223479098003E-9</v>
+        <v>-2413800.3254847699</v>
       </c>
       <c r="C15">
-        <v>-2.6285707176725901E-10</v>
-      </c>
-      <c r="D15" s="1">
-        <v>-1.3076134131136401E-10</v>
+        <v>-959914.64377220999</v>
+      </c>
+      <c r="D15">
+        <v>-635876.06149440003</v>
       </c>
       <c r="E15">
-        <v>-2.29376184301506E-10</v>
+        <v>-617966.49983508</v>
       </c>
       <c r="F15">
-        <v>-5.5242149522427598E-11</v>
+        <v>-301512.08818551898</v>
       </c>
       <c r="G15">
-        <v>1.15165594031759E-10</v>
-      </c>
-      <c r="H15" s="1">
-        <v>2.0761492224483099E-10</v>
+        <v>4208029.0768353697</v>
+      </c>
+      <c r="H15">
+        <v>658402.55558669101</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
@@ -1741,126 +1733,126 @@
         <v>-328223.45019667398</v>
       </c>
       <c r="C16">
-        <v>-122959.306736447</v>
-      </c>
-      <c r="D16" s="1">
-        <v>-70596.259860167207</v>
+        <v>-119601.88714965701</v>
+      </c>
+      <c r="D16">
+        <v>-64893.179008151899</v>
       </c>
       <c r="E16">
-        <v>126856.071980857</v>
+        <v>115190.337245332</v>
       </c>
       <c r="F16">
-        <v>-26408.772546560002</v>
+        <v>-22153.694545501501</v>
       </c>
       <c r="G16">
         <v>20992555.073462401</v>
       </c>
-      <c r="H16" s="1">
-        <v>96550.534189887301</v>
+      <c r="H16">
+        <v>97448.192604155498</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B17">
-        <v>-2413800.3254847699</v>
+        <v>-960822.21716641996</v>
       </c>
       <c r="C17">
-        <v>-946129.99674836895</v>
-      </c>
-      <c r="D17" s="1">
-        <v>-631581.80410028005</v>
+        <v>7496.8653507312201</v>
+      </c>
+      <c r="D17">
+        <v>16875.264918780998</v>
       </c>
       <c r="E17">
-        <v>-610288.68618402397</v>
+        <v>12650.7173616408</v>
       </c>
       <c r="F17">
-        <v>-300402.87981592002</v>
+        <v>29213.7087853915</v>
       </c>
       <c r="G17">
-        <v>4208029.0768353697</v>
-      </c>
-      <c r="H17" s="1">
-        <v>645727.11693244905</v>
+        <v>128618.55793744</v>
+      </c>
+      <c r="H17">
+        <v>21716.843434660299</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B18">
-        <v>-960822.21716641996</v>
+        <v>-6114613.0747147296</v>
       </c>
       <c r="C18">
-        <v>7585.3961334362402</v>
-      </c>
-      <c r="D18" s="1">
-        <v>17516.231309855499</v>
+        <v>-2679989.9160323502</v>
+      </c>
+      <c r="D18">
+        <v>-1787304.15427708</v>
       </c>
       <c r="E18">
-        <v>12569.766403766</v>
+        <v>-1706921.0758665199</v>
       </c>
       <c r="F18">
-        <v>29928.207823104502</v>
+        <v>-720660.96095113596</v>
       </c>
       <c r="G18">
-        <v>128618.55793744</v>
-      </c>
-      <c r="H18" s="1">
-        <v>22342.811689668299</v>
+        <v>8209638.6904595597</v>
+      </c>
+      <c r="H18">
+        <v>1959328.95508122</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="B19">
-        <v>-0.17456829613396899</v>
+        <v>-1896907.4517372099</v>
       </c>
       <c r="C19">
-        <v>3.3421961147595499E-3</v>
-      </c>
-      <c r="D19" s="1">
-        <v>8.6686892467750208E-3</v>
+        <v>-527854.22681722604</v>
+      </c>
+      <c r="D19">
+        <v>-278278.75612729299</v>
       </c>
       <c r="E19">
-        <v>1.1793427037630699E-2</v>
+        <v>264114.58349585498</v>
       </c>
       <c r="F19">
-        <v>1.77135509937369E-2</v>
+        <v>-108853.31889198899</v>
       </c>
       <c r="G19">
-        <v>9.9656857143405803E-2</v>
-      </c>
-      <c r="H19" s="1">
-        <v>1.43713548789773E-2</v>
+        <v>60701825.714204498</v>
+      </c>
+      <c r="H19">
+        <v>419000.90792523802</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B20">
-        <v>-49494.423254303998</v>
+        <v>-2655196.6584520498</v>
       </c>
       <c r="C20">
-        <v>-4489.9265139219997</v>
-      </c>
-      <c r="D20" s="1">
-        <v>-2061.9313811914699</v>
+        <v>19726.4398593687</v>
+      </c>
+      <c r="D20">
+        <v>43255.658965787603</v>
       </c>
       <c r="E20">
-        <v>-3348.1004067161098</v>
+        <v>38551.666220896899</v>
       </c>
       <c r="F20">
-        <v>-961.07246189170598</v>
+        <v>93272.888079804994</v>
       </c>
       <c r="G20">
-        <v>20322.932531290298</v>
-      </c>
-      <c r="H20" s="1">
-        <v>3528.8540520302899</v>
+        <v>270006.78528565902</v>
+      </c>
+      <c r="H20">
+        <v>73546.448220436301</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
@@ -1871,48 +1863,48 @@
         <v>-377670.22932951699</v>
       </c>
       <c r="C21">
-        <v>-23070.420706802801</v>
-      </c>
-      <c r="D21" s="1">
-        <v>-10559.8753436724</v>
+        <v>-28115.042353802601</v>
+      </c>
+      <c r="D21">
+        <v>-12317.803306223601</v>
       </c>
       <c r="E21">
-        <v>-20837.793838084799</v>
+        <v>-25307.878882808702</v>
       </c>
       <c r="F21">
-        <v>-4427.6546782315299</v>
+        <v>-4744.4685546016899</v>
       </c>
       <c r="G21">
         <v>120682.438633709</v>
       </c>
-      <c r="H21" s="1">
-        <v>18642.766028571201</v>
+      <c r="H21">
+        <v>23370.573799200902</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B22">
-        <v>-24388.100428040001</v>
+        <v>-49494.423254303998</v>
       </c>
       <c r="C22">
-        <v>148.08478887573199</v>
-      </c>
-      <c r="D22" s="1">
-        <v>372.02525504653499</v>
+        <v>-4718.1365007653803</v>
+      </c>
+      <c r="D22">
+        <v>-2211.2455736255001</v>
       </c>
       <c r="E22">
-        <v>735.44609378752796</v>
+        <v>-3622.02563760765</v>
       </c>
       <c r="F22">
-        <v>1056.6683528168101</v>
+        <v>-1001.8572898370001</v>
       </c>
       <c r="G22">
-        <v>17424.849829694998</v>
-      </c>
-      <c r="H22" s="1">
-        <v>908.583563941075</v>
+        <v>20322.932531290298</v>
+      </c>
+      <c r="H22">
+        <v>3716.2792109283801</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
@@ -1923,22 +1915,22 @@
         <v>-10226.4804291401</v>
       </c>
       <c r="C23">
-        <v>-1914.8788658890101</v>
-      </c>
-      <c r="D23" s="1">
+        <v>-1957.19118759001</v>
+      </c>
+      <c r="D23">
         <v>-1024.6726018899101</v>
       </c>
       <c r="E23">
-        <v>-901.33478403538095</v>
+        <v>-969.58137171118597</v>
       </c>
       <c r="F23">
-        <v>-552.26251553676502</v>
+        <v>-568.58759229122597</v>
       </c>
       <c r="G23">
         <v>50090.705827621001</v>
       </c>
-      <c r="H23" s="1">
-        <v>1362.61635035225</v>
+      <c r="H23">
+        <v>1388.60359529879</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
@@ -1949,238 +1941,233 @@
         <v>-27077.112463310001</v>
       </c>
       <c r="C24">
-        <v>877.56246713866005</v>
-      </c>
-      <c r="D24" s="1">
-        <v>2146.1772803377498</v>
+        <v>894.395313366653</v>
+      </c>
+      <c r="D24">
+        <v>2302.8228213206498</v>
       </c>
       <c r="E24">
-        <v>3728.5403099577802</v>
+        <v>4140.0817677973901</v>
       </c>
       <c r="F24">
-        <v>4903.6287919079296</v>
+        <v>5537.6318641719799</v>
       </c>
       <c r="G24">
-        <v>38856.569517520002</v>
-      </c>
-      <c r="H24" s="1">
-        <v>4026.0663247692701</v>
+        <v>88074.1936271101</v>
+      </c>
+      <c r="H24">
+        <v>4643.2365508053199</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B25">
-        <v>-9758.1557759256993</v>
+        <v>-24933.6949309505</v>
       </c>
       <c r="C25">
-        <v>387.47027319397802</v>
-      </c>
-      <c r="D25" s="1">
-        <v>838.07009873634001</v>
+        <v>155.359902720419</v>
+      </c>
+      <c r="D25">
+        <v>379.43337360957503</v>
       </c>
       <c r="E25">
-        <v>846.70168907194898</v>
+        <v>818.11363325768502</v>
       </c>
       <c r="F25">
-        <v>1344.38613336049</v>
+        <v>1085.5487175831699</v>
       </c>
       <c r="G25">
-        <v>5136.6511162331999</v>
-      </c>
-      <c r="H25" s="1">
-        <v>956.91586016651002</v>
+        <v>20174.297787889001</v>
+      </c>
+      <c r="H25">
+        <v>930.18881486275495</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B26">
-        <v>-8570.4300545331098</v>
+        <v>-1.6615631677728501E-2</v>
       </c>
       <c r="C26">
-        <v>0.42416157391977899</v>
-      </c>
-      <c r="D26" s="1">
-        <v>1.70083860190352</v>
+        <v>1.4882820110672899E-3</v>
+      </c>
+      <c r="D26">
+        <v>5.0759174528211002E-3</v>
       </c>
       <c r="E26">
-        <v>-61.240943526370302</v>
+        <v>9.4630754540868198E-3</v>
       </c>
       <c r="F26">
-        <v>4.5178147681234799</v>
+        <v>1.2179799604918501E-2</v>
       </c>
       <c r="G26">
-        <v>101.09513226553</v>
-      </c>
-      <c r="H26" s="1">
-        <v>4.0936531942037</v>
+        <v>9.2757985648146996E-2</v>
+      </c>
+      <c r="H26">
+        <v>1.0691517593851301E-2</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="B27">
-        <v>-2.3132318976992798</v>
+        <v>-10.902772888114701</v>
       </c>
       <c r="C27">
-        <v>4.1076435872492302E-2</v>
-      </c>
-      <c r="D27" s="1">
-        <v>0.21785880391367199</v>
+        <v>0.16802733201244899</v>
+      </c>
+      <c r="D27">
+        <v>0.233206263228</v>
       </c>
       <c r="E27">
-        <v>0.43858688522135097</v>
+        <v>0.125253556633626</v>
       </c>
       <c r="F27">
-        <v>0.58613542621919201</v>
+        <v>0.26897538416945099</v>
       </c>
       <c r="G27">
-        <v>15.8968435637341</v>
-      </c>
-      <c r="H27" s="1">
-        <v>0.54505899034670002</v>
+        <v>0.37610096893310202</v>
+      </c>
+      <c r="H27">
+        <v>0.10094805215700201</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="B28">
-        <v>-1580.2621433636</v>
+        <v>-0.17941493697866001</v>
       </c>
       <c r="C28">
-        <v>-339.69554391610802</v>
-      </c>
-      <c r="D28" s="1">
-        <v>-189.58711128780399</v>
+        <v>-2.9084871528647301E-2</v>
+      </c>
+      <c r="D28">
+        <v>-1.3740523228799499E-2</v>
       </c>
       <c r="E28">
-        <v>-63.835822684856403</v>
+        <v>-2.09181248637458E-2</v>
       </c>
       <c r="F28">
-        <v>-89.157575940135501</v>
+        <v>-6.9365472359352396E-3</v>
       </c>
       <c r="G28">
-        <v>13089.374917285601</v>
-      </c>
-      <c r="H28" s="1">
-        <v>250.53796797597201</v>
+        <v>1.2524722804679899E-2</v>
+      </c>
+      <c r="H28">
+        <v>2.2148324292712102E-2</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="B29">
-        <v>-10922.9246092468</v>
+        <v>-0.59582971146590002</v>
       </c>
       <c r="C29">
-        <v>-2041.82859508962</v>
-      </c>
-      <c r="D29" s="1">
-        <v>-1356.7458490015799</v>
+        <v>1.1985228712229999E-2</v>
+      </c>
+      <c r="D29">
+        <v>1.8918221547869998E-2</v>
       </c>
       <c r="E29">
-        <v>-1452.9288736014601</v>
+        <v>1.84616772291127E-2</v>
       </c>
       <c r="F29">
-        <v>-476.53179180429203</v>
+        <v>2.8165491810632801E-2</v>
       </c>
       <c r="G29">
-        <v>2917.4913152019199</v>
-      </c>
-      <c r="H29" s="1">
-        <v>1565.29680328532</v>
+        <v>8.0481365346869699E-2</v>
+      </c>
+      <c r="H29">
+        <v>1.61802630984028E-2</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="B30">
-        <v>-549.29940596082395</v>
+        <v>-9.6695681519959997E-2</v>
       </c>
       <c r="C30">
-        <v>2.70079410225051</v>
-      </c>
-      <c r="D30" s="1">
-        <v>7.9080700321476503</v>
+        <v>-2.3567226731304899E-2</v>
+      </c>
+      <c r="D30">
+        <v>-1.40690270800074E-2</v>
       </c>
       <c r="E30">
-        <v>4.4738739257832902</v>
+        <v>1.9695437796516798E-3</v>
       </c>
       <c r="F30">
-        <v>16.557790902260798</v>
+        <v>-6.4800827059847497E-3</v>
       </c>
       <c r="G30">
-        <v>83.585205423730997</v>
-      </c>
-      <c r="H30" s="1">
-        <v>13.8569968000103</v>
+        <v>2.4218736664283398</v>
+      </c>
+      <c r="H30">
+        <v>1.7087144025320199E-2</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="B31">
-        <v>-2.6337430704085401E-10</v>
+        <v>-0.16630544948169099</v>
       </c>
       <c r="C31">
-        <v>0</v>
-      </c>
-      <c r="D31" s="1">
-        <v>8.8012017179612599E-11</v>
+        <v>1.25750804166048E-3</v>
+      </c>
+      <c r="D31">
+        <v>3.2041883374801798E-3</v>
       </c>
       <c r="E31">
-        <v>2.7363506429837598E-10</v>
+        <v>2.6618285314725198E-3</v>
       </c>
       <c r="F31">
-        <v>2.6337430704085401E-10</v>
+        <v>6.3173473067235199E-3</v>
       </c>
       <c r="G31">
-        <v>8.6595883967004301E-9</v>
-      </c>
-      <c r="H31" s="1">
-        <v>2.6337430704085401E-10</v>
+        <v>2.9198909318277001E-2</v>
+      </c>
+      <c r="H31">
+        <v>5.0598392650630496E-3</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B32">
-        <v>-57.1250935443854</v>
+        <v>-0.17456829613396899</v>
       </c>
       <c r="C32">
-        <v>1.6652630663305299</v>
+        <v>3.38077469622208E-3</v>
       </c>
       <c r="D32" s="1">
-        <v>5.2726691068816303</v>
+        <v>8.8386555109915502E-3</v>
       </c>
       <c r="E32">
-        <v>7.0672674183698598</v>
+        <v>1.21249039855593E-2</v>
       </c>
       <c r="F32">
-        <v>10.9034264256236</v>
+        <v>1.8358907505559598E-2</v>
       </c>
       <c r="G32">
-        <v>69.407146696675994</v>
-      </c>
-      <c r="H32" s="1">
-        <v>9.2381633592931198</v>
+        <v>0.10631107883518701</v>
+      </c>
+      <c r="H32">
+        <v>1.49781328093375E-2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1" xr:uid="{00000000-0001-0000-0100-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H32">
-      <sortCondition ref="A1"/>
-    </sortState>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -2190,9 +2177,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H32"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="16.54296875" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -2222,262 +2206,262 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="B2">
-        <v>-0.14860484985671199</v>
+        <v>-0.41858434356751401</v>
       </c>
       <c r="C2">
-        <v>1.9490019393118699E-3</v>
-      </c>
-      <c r="D2" s="1">
-        <v>2.6204223649637102E-3</v>
+        <v>4.3107037782154398E-2</v>
+      </c>
+      <c r="D2">
+        <v>7.73478313709621E-2</v>
       </c>
       <c r="E2">
-        <v>1.19479381540083E-3</v>
+        <v>9.1659908689015607E-2</v>
       </c>
       <c r="F2">
-        <v>2.9467728121879001E-3</v>
+        <v>0.15479777342913401</v>
       </c>
       <c r="G2">
-        <v>5.1015462550860801E-3</v>
-      </c>
-      <c r="H2" s="1">
-        <v>9.9777087287602996E-4</v>
+        <v>0.291433638360449</v>
+      </c>
+      <c r="H2">
+        <v>0.111690735646979</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="B3">
-        <v>-2.81704952718385E-2</v>
+        <v>-0.46702043761506801</v>
       </c>
       <c r="C3">
-        <v>-1.80087849567859E-2</v>
-      </c>
-      <c r="D3" s="1">
-        <v>-1.32776914511595E-2</v>
+        <v>4.8733982209173202E-2</v>
+      </c>
+      <c r="D3">
+        <v>8.4635174678707195E-2</v>
       </c>
       <c r="E3">
-        <v>-9.3404081671333E-3</v>
+        <v>9.7903666187760696E-2</v>
       </c>
       <c r="F3">
-        <v>-8.2083457714323699E-3</v>
+        <v>0.16511281028109401</v>
       </c>
       <c r="G3">
-        <v>0.33835024044667</v>
-      </c>
-      <c r="H3" s="1">
-        <v>9.80043918535356E-3</v>
+        <v>0.30361263445976999</v>
+      </c>
+      <c r="H3">
+        <v>0.116378828071921</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="B4">
-        <v>-5.4002372350003602E-2</v>
+        <v>-0.49754810213803202</v>
       </c>
       <c r="C4">
-        <v>1.2841033999118599E-3</v>
-      </c>
-      <c r="D4" s="1">
-        <v>1.9481114881255699E-3</v>
+        <v>5.1050189660211798E-2</v>
+      </c>
+      <c r="D4">
+        <v>8.7497236265813794E-2</v>
       </c>
       <c r="E4">
-        <v>1.6071213898132301E-3</v>
+        <v>0.100340565112505</v>
       </c>
       <c r="F4">
-        <v>2.5141895592179502E-3</v>
+        <v>0.168515205326253</v>
       </c>
       <c r="G4">
-        <v>4.2766152783315602E-3</v>
-      </c>
-      <c r="H4" s="1">
-        <v>1.23008615930609E-3</v>
+        <v>0.308433527396614</v>
+      </c>
+      <c r="H4">
+        <v>0.11746501566604101</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="B5">
-        <v>-2.2742259454224801E-2</v>
+        <v>-1.48906419380108</v>
       </c>
       <c r="C5">
-        <v>-1.4181327187173499E-2</v>
-      </c>
-      <c r="D5" s="1">
-        <v>-1.03609506603273E-2</v>
+        <v>-0.79567529944270898</v>
+      </c>
+      <c r="D5">
+        <v>-0.55527256900194399</v>
       </c>
       <c r="E5">
-        <v>-6.9445568548184696E-3</v>
+        <v>-0.55729763459737902</v>
       </c>
       <c r="F5">
-        <v>-6.2114344469784699E-3</v>
+        <v>-0.33949898579806398</v>
       </c>
       <c r="G5">
-        <v>0.30776312874047002</v>
-      </c>
-      <c r="H5" s="1">
-        <v>7.9698927401949896E-3</v>
+        <v>0.57336331839389998</v>
+      </c>
+      <c r="H5">
+        <v>0.456176313644645</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B6">
-        <v>-0.24793296927664699</v>
+        <v>-1.4920496314473599</v>
       </c>
       <c r="C6">
-        <v>3.9295348884278998E-2</v>
-      </c>
-      <c r="D6" s="1">
-        <v>6.9146526326355998E-2</v>
+        <v>-0.79939092497562103</v>
+      </c>
+      <c r="D6">
+        <v>-0.55876719386537999</v>
       </c>
       <c r="E6">
-        <v>8.5885368751465199E-2</v>
+        <v>-0.55973456963127999</v>
       </c>
       <c r="F6">
-        <v>0.14323823847025299</v>
+        <v>-0.34210249719289598</v>
       </c>
       <c r="G6">
-        <v>0.28233165622927597</v>
-      </c>
-      <c r="H6" s="1">
-        <v>0.103942889585974</v>
+        <v>0.59059396563195599</v>
+      </c>
+      <c r="H6">
+        <v>0.45728842778272499</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="B7">
-        <v>-0.25293638742417701</v>
+        <v>-0.55216979913414999</v>
       </c>
       <c r="C7">
-        <v>4.0001671477317501E-2</v>
-      </c>
-      <c r="D7" s="1">
-        <v>7.0522538033236395E-2</v>
+        <v>5.5864342476944898E-2</v>
+      </c>
+      <c r="D7">
+        <v>9.3572616683822094E-2</v>
       </c>
       <c r="E7">
-        <v>8.68386895605434E-2</v>
+        <v>0.10565551676307899</v>
       </c>
       <c r="F7">
-        <v>0.14417791494965701</v>
+        <v>0.176414959475861</v>
       </c>
       <c r="G7">
-        <v>0.283769259002909</v>
-      </c>
-      <c r="H7" s="1">
-        <v>0.10417624347234</v>
+        <v>0.31788062985976201</v>
+      </c>
+      <c r="H7">
+        <v>0.120550616998916</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B8">
-        <v>-1.62095784804419</v>
+        <v>-0.49769247781794101</v>
       </c>
       <c r="C8">
-        <v>-0.87490464378058697</v>
-      </c>
-      <c r="D8" s="1">
-        <v>-0.62712167097362403</v>
+        <v>5.1153671781850603E-2</v>
+      </c>
+      <c r="D8">
+        <v>8.7574398517951998E-2</v>
       </c>
       <c r="E8">
-        <v>-0.61127217353181396</v>
+        <v>0.100428180750812</v>
       </c>
       <c r="F8">
-        <v>-0.37104249147701801</v>
+        <v>0.16854767823855801</v>
       </c>
       <c r="G8">
-        <v>0.710551980852134</v>
-      </c>
-      <c r="H8" s="1">
-        <v>0.50386215230356901</v>
+        <v>0.30844867656865799</v>
+      </c>
+      <c r="H8">
+        <v>0.117394006456707</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B9">
-        <v>-1.62367540179461</v>
+        <v>-1.14440295861939E-5</v>
       </c>
       <c r="C9">
-        <v>-0.87923652214710302</v>
-      </c>
-      <c r="D9" s="1">
-        <v>-0.63001625714675902</v>
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>3.8233542785093303E-6</v>
       </c>
       <c r="E9">
-        <v>-0.61365594671180101</v>
+        <v>1.5452364213268801E-5</v>
       </c>
       <c r="F9">
-        <v>-0.37346280210830402</v>
+        <v>1.33666473656202E-5</v>
       </c>
       <c r="G9">
-        <v>0.72778286266985504</v>
-      </c>
-      <c r="H9" s="1">
-        <v>0.50577372003879895</v>
+        <v>3.7957322504667001E-4</v>
+      </c>
+      <c r="H9">
+        <v>1.33666473656202E-5</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="B10">
-        <v>-0.54327438952671803</v>
+        <v>-0.30336652079266202</v>
       </c>
       <c r="C10">
-        <v>1.73750001895514E-2</v>
-      </c>
-      <c r="D10" s="1">
-        <v>2.4654161775351301E-2</v>
+        <v>5.0071132268793499E-2</v>
+      </c>
+      <c r="D10">
+        <v>8.5280358453542093E-2</v>
       </c>
       <c r="E10">
-        <v>1.7582113294618298E-2</v>
+        <v>0.100165511918484</v>
       </c>
       <c r="F10">
-        <v>3.0238154062934699E-2</v>
+        <v>0.16216762286240999</v>
       </c>
       <c r="G10">
-        <v>4.3013549499488803E-2</v>
-      </c>
-      <c r="H10" s="1">
-        <v>1.28631538733833E-2</v>
+        <v>0.29592108584471999</v>
+      </c>
+      <c r="H10">
+        <v>0.112096490593617</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B11">
-        <v>-0.41858434356751401</v>
+        <v>-1.63930897665085</v>
       </c>
       <c r="C11">
-        <v>4.2342092438868099E-2</v>
-      </c>
-      <c r="D11" s="1">
-        <v>7.39324493066644E-2</v>
+        <v>-0.96472617963709995</v>
+      </c>
+      <c r="D11">
+        <v>-0.67125227562615197</v>
       </c>
       <c r="E11">
-        <v>8.8550504360448007E-2</v>
+        <v>-0.66007511260384999</v>
       </c>
       <c r="F11">
-        <v>0.14996542127119999</v>
+        <v>-0.411566297152552</v>
       </c>
       <c r="G11">
-        <v>0.291433638360449</v>
-      </c>
-      <c r="H11" s="1">
-        <v>0.107623328832331</v>
+        <v>1.0766798264361399</v>
+      </c>
+      <c r="H11">
+        <v>0.55315988248454795</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -2488,100 +2472,100 @@
         <v>-1.6365909860016701</v>
       </c>
       <c r="C12">
-        <v>-0.903906128234929</v>
-      </c>
-      <c r="D12" s="1">
-        <v>-0.64698505053863398</v>
+        <v>-0.961268199789719</v>
+      </c>
+      <c r="D12">
+        <v>-0.66811011783535701</v>
       </c>
       <c r="E12">
-        <v>-0.62363156738738101</v>
+        <v>-0.65763822411335804</v>
       </c>
       <c r="F12">
-        <v>-0.38731144787809502</v>
+        <v>-0.40929757832428199</v>
       </c>
       <c r="G12">
         <v>1.04615306991544</v>
       </c>
-      <c r="H12" s="1">
-        <v>0.51659468035683398</v>
+      <c r="H12">
+        <v>0.55197062146543696</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13">
-        <v>-0.30842398395728499</v>
+        <v>-0.31324587412855798</v>
       </c>
       <c r="C13">
-        <v>-0.16223907778831401</v>
-      </c>
-      <c r="D13" s="1">
-        <v>-8.4427833774295594E-2</v>
+        <v>-0.17226728158447399</v>
+      </c>
+      <c r="D13">
+        <v>-9.0488829998078807E-2</v>
       </c>
       <c r="E13">
-        <v>-9.7038194466467803E-2</v>
+        <v>-0.10276196876119301</v>
       </c>
       <c r="F13">
-        <v>-5.0577164478872803E-2</v>
+        <v>-5.3135806120946101E-2</v>
       </c>
       <c r="G13">
-        <v>0.49754713986554</v>
-      </c>
-      <c r="H13" s="1">
-        <v>0.111661913309441</v>
+        <v>0.52807388501379104</v>
+      </c>
+      <c r="H13">
+        <v>0.11913147546352799</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B14">
-        <v>-1.63930897665085</v>
+        <v>-0.30842398395728499</v>
       </c>
       <c r="C14">
-        <v>-0.90754794742311096</v>
-      </c>
-      <c r="D14" s="1">
-        <v>-0.65019960039952696</v>
+        <v>-0.168499475692581</v>
+      </c>
+      <c r="D14">
+        <v>-8.7500569340432002E-2</v>
       </c>
       <c r="E14">
-        <v>-0.62601538318542704</v>
+        <v>-0.100325199296195</v>
       </c>
       <c r="F14">
-        <v>-0.38973179451180201</v>
+        <v>-5.1048273623686101E-2</v>
       </c>
       <c r="G14">
-        <v>1.0766798264361399</v>
-      </c>
-      <c r="H14" s="1">
-        <v>0.51781615291131</v>
+        <v>0.49754713986554</v>
+      </c>
+      <c r="H14">
+        <v>0.11745120206889401</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B15">
-        <v>-0.31324587412855798</v>
+        <v>-1.6235494882855099</v>
       </c>
       <c r="C15">
-        <v>-0.16632298372411999</v>
-      </c>
-      <c r="D15" s="1">
-        <v>-8.7188215745126002E-2</v>
+        <v>-0.94534538854503503</v>
+      </c>
+      <c r="D15">
+        <v>-0.65048229152938997</v>
       </c>
       <c r="E15">
-        <v>-9.9421891097740897E-2</v>
+        <v>-0.64686983702138501</v>
       </c>
       <c r="F15">
-        <v>-5.2930390177041702E-2</v>
+        <v>-0.398855750772941</v>
       </c>
       <c r="G15">
-        <v>0.52807388501379104</v>
-      </c>
-      <c r="H15" s="1">
-        <v>0.11339259354707899</v>
+        <v>0.78766124892363598</v>
+      </c>
+      <c r="H15">
+        <v>0.54648963777209403</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
@@ -2592,126 +2576,126 @@
         <v>-1.6208305330192501</v>
       </c>
       <c r="C16">
-        <v>-0.87592256487958498</v>
-      </c>
-      <c r="D16" s="1">
-        <v>-0.62818954158376705</v>
+        <v>-0.94248833479160099</v>
+      </c>
+      <c r="D16">
+        <v>-0.64664125663799099</v>
       </c>
       <c r="E16">
-        <v>-0.61085981668876099</v>
+        <v>-0.64443296640293202</v>
       </c>
       <c r="F16">
-        <v>-0.37183391022564599</v>
+        <v>-0.396586774583566</v>
       </c>
       <c r="G16">
         <v>0.770429355901872</v>
       </c>
-      <c r="H16" s="1">
-        <v>0.50408865465393804</v>
+      <c r="H16">
+        <v>0.54590156020803404</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B17">
-        <v>-1.6235494882855099</v>
+        <v>-0.448672280093454</v>
       </c>
       <c r="C17">
-        <v>-0.88055092998654005</v>
-      </c>
-      <c r="D17" s="1">
-        <v>-0.63108434520736301</v>
+        <v>1.7571322346512701E-2</v>
+      </c>
+      <c r="D17">
+        <v>2.4300101989756899E-2</v>
       </c>
       <c r="E17">
-        <v>-0.613243607382287</v>
+        <v>1.85202074923667E-2</v>
       </c>
       <c r="F17">
-        <v>-0.374254335681657</v>
+        <v>3.0045269533624401E-2</v>
       </c>
       <c r="G17">
-        <v>0.78766124892363598</v>
-      </c>
-      <c r="H17" s="1">
-        <v>0.50629659430488305</v>
+        <v>4.3186208229539301E-2</v>
+      </c>
+      <c r="H17">
+        <v>1.24739471871117E-2</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B18">
-        <v>-0.448672280093454</v>
+        <v>-1.62367540179461</v>
       </c>
       <c r="C18">
-        <v>1.7189251384167901E-2</v>
-      </c>
-      <c r="D18" s="1">
-        <v>2.38718931524564E-2</v>
+        <v>-0.94551739947640301</v>
+      </c>
+      <c r="D18">
+        <v>-0.65023147255580804</v>
       </c>
       <c r="E18">
-        <v>1.7994470113082198E-2</v>
+        <v>-0.64725682103965698</v>
       </c>
       <c r="F18">
-        <v>2.9825086086926099E-2</v>
+        <v>-0.39906755973121599</v>
       </c>
       <c r="G18">
-        <v>4.3186208229539301E-2</v>
-      </c>
-      <c r="H18" s="1">
-        <v>1.2635834702758199E-2</v>
+        <v>0.72778286266985504</v>
+      </c>
+      <c r="H18">
+        <v>0.54644983974518702</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="B19">
-        <v>-0.25274767612922699</v>
+        <v>-1.62095784804419</v>
       </c>
       <c r="C19">
-        <v>3.97421893687082E-2</v>
-      </c>
-      <c r="D19" s="1">
-        <v>6.9730247226796202E-2</v>
+        <v>-0.942090276399008</v>
+      </c>
+      <c r="D19">
+        <v>-0.64638995113803199</v>
       </c>
       <c r="E19">
-        <v>8.6192553092660704E-2</v>
+        <v>-0.64481997298872995</v>
       </c>
       <c r="F19">
-        <v>0.14362799103913401</v>
+        <v>-0.39679919723379498</v>
       </c>
       <c r="G19">
-        <v>0.28278134028027102</v>
-      </c>
-      <c r="H19" s="1">
-        <v>0.10388580167042499</v>
+        <v>0.710551980852134</v>
+      </c>
+      <c r="H19">
+        <v>0.54529107916521302</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B20">
-        <v>-3.10816058236019E-2</v>
+        <v>-0.54327438952671803</v>
       </c>
       <c r="C20">
-        <v>-2.4185643917162799E-3</v>
-      </c>
-      <c r="D20" s="1">
-        <v>-1.96708043910521E-3</v>
+        <v>1.7710445181594502E-2</v>
+      </c>
+      <c r="D20">
+        <v>2.5077353831022699E-2</v>
       </c>
       <c r="E20">
-        <v>-1.9507805605932099E-3</v>
+        <v>1.8133202834281398E-2</v>
       </c>
       <c r="F20">
-        <v>-1.3035063501510801E-3</v>
+        <v>3.0447376269103699E-2</v>
       </c>
       <c r="G20">
-        <v>4.7143494163548504E-3</v>
-      </c>
-      <c r="H20" s="1">
-        <v>1.1150580415652E-3</v>
+        <v>4.3013549499488803E-2</v>
+      </c>
+      <c r="H20">
+        <v>1.2736931087509199E-2</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
@@ -2722,48 +2706,48 @@
         <v>-1.5304555190742499</v>
       </c>
       <c r="C21">
-        <v>-0.76793145386489503</v>
-      </c>
-      <c r="D21" s="1">
-        <v>-0.55064579053353901</v>
+        <v>-0.82980878457982898</v>
+      </c>
+      <c r="D21">
+        <v>-0.57005260498946897</v>
       </c>
       <c r="E21">
-        <v>-0.53827779592060598</v>
+        <v>-0.57045664465146495</v>
       </c>
       <c r="F21">
-        <v>-0.31163310401530597</v>
+        <v>-0.33192011184883002</v>
       </c>
       <c r="G21">
         <v>0.67226156807116499</v>
       </c>
-      <c r="H21" s="1">
-        <v>0.456298349849589</v>
+      <c r="H21">
+        <v>0.49788867273100001</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B22">
-        <v>-8.2798487938713805E-2</v>
+        <v>-3.10816058236019E-2</v>
       </c>
       <c r="C22">
-        <v>3.10168767341974E-2</v>
-      </c>
-      <c r="D22" s="1">
-        <v>4.3993678526403998E-2</v>
+        <v>-2.4475201014513299E-3</v>
+      </c>
+      <c r="D22">
+        <v>-1.9971387955881599E-3</v>
       </c>
       <c r="E22">
-        <v>3.9483040179590499E-2</v>
+        <v>-1.9817085152644899E-3</v>
       </c>
       <c r="F22">
-        <v>5.5198186202733299E-2</v>
+        <v>-1.41896099906369E-3</v>
       </c>
       <c r="G22">
-        <v>8.8810947159032094E-2</v>
-      </c>
-      <c r="H22" s="1">
-        <v>2.4181309468535899E-2</v>
+        <v>4.7143494163548504E-3</v>
+      </c>
+      <c r="H22">
+        <v>1.0285591023876401E-3</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
@@ -2771,25 +2755,25 @@
         <v>29</v>
       </c>
       <c r="B23">
-        <v>-4.8478213754390397E-3</v>
+        <v>-5.0839370130360004E-3</v>
       </c>
       <c r="C23">
-        <v>-3.1726301701927601E-3</v>
-      </c>
-      <c r="D23" s="1">
+        <v>-3.1931429015509302E-3</v>
+      </c>
+      <c r="D23">
         <v>-2.6131899990202699E-3</v>
       </c>
       <c r="E23">
-        <v>-1.6440972225634301E-3</v>
+        <v>-1.7071796883465901E-3</v>
       </c>
       <c r="F23">
-        <v>-1.75458795270711E-3</v>
+        <v>-1.7636616333806001E-3</v>
       </c>
       <c r="G23">
         <v>6.6014674854127306E-2</v>
       </c>
-      <c r="H23" s="1">
-        <v>1.4180422174856499E-3</v>
+      <c r="H23">
+        <v>1.4294812681703299E-3</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
@@ -2797,241 +2781,236 @@
         <v>30</v>
       </c>
       <c r="B24">
-        <v>-8.2798494102560599E-2</v>
+        <v>-0.11002335540774399</v>
       </c>
       <c r="C24">
-        <v>3.1016895169627998E-2</v>
-      </c>
-      <c r="D24" s="1">
-        <v>4.3993620888255397E-2</v>
+        <v>3.1510550602938101E-2</v>
+      </c>
+      <c r="D24">
+        <v>4.5124139558218902E-2</v>
       </c>
       <c r="E24">
-        <v>3.9483041793669002E-2</v>
+        <v>3.99745039505685E-2</v>
       </c>
       <c r="F24">
-        <v>5.5198127757886802E-2</v>
+        <v>5.6595742887823097E-2</v>
       </c>
       <c r="G24">
         <v>8.8810989625529996E-2</v>
       </c>
-      <c r="H24" s="1">
-        <v>2.41812325882588E-2</v>
+      <c r="H24">
+        <v>2.5085192284885E-2</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B25">
-        <v>-0.30336652079266202</v>
+        <v>-0.110023321272551</v>
       </c>
       <c r="C25">
-        <v>4.96150128172562E-2</v>
-      </c>
-      <c r="D25" s="1">
-        <v>8.2528588037484293E-2</v>
+        <v>3.1510566598484203E-2</v>
+      </c>
+      <c r="D25">
+        <v>4.5124118093892399E-2</v>
       </c>
       <c r="E25">
-        <v>9.6934283482960501E-2</v>
+        <v>3.9974502832495901E-2</v>
       </c>
       <c r="F25">
-        <v>0.15834816676924399</v>
+        <v>5.6595737733422198E-2</v>
       </c>
       <c r="G25">
-        <v>0.29592108584471999</v>
-      </c>
-      <c r="H25" s="1">
-        <v>0.108733153951988</v>
+        <v>8.8810947159032094E-2</v>
+      </c>
+      <c r="H25">
+        <v>2.5085171134937901E-2</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B26">
-        <v>-0.49754810213803202</v>
+        <v>-0.24793296927664699</v>
       </c>
       <c r="C26">
-        <v>5.0641793141816098E-2</v>
-      </c>
-      <c r="D26" s="1">
-        <v>8.4431179062730996E-2</v>
+        <v>3.9445283265120402E-2</v>
+      </c>
+      <c r="D26">
+        <v>7.15988524121971E-2</v>
       </c>
       <c r="E26">
-        <v>9.7050019865481799E-2</v>
+        <v>8.8807296286072201E-2</v>
       </c>
       <c r="F26">
-        <v>0.16225861587888299</v>
+        <v>0.14711048709017999</v>
       </c>
       <c r="G26">
-        <v>0.308433527396614</v>
-      </c>
-      <c r="H26" s="1">
-        <v>0.111616822737067</v>
+        <v>0.28233165622927597</v>
+      </c>
+      <c r="H26">
+        <v>0.10766520382505999</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="B27">
-        <v>-0.49769247781794101</v>
+        <v>-0.14860484985671199</v>
       </c>
       <c r="C27">
-        <v>5.0745254021424602E-2</v>
-      </c>
-      <c r="D27" s="1">
-        <v>8.4501317952122595E-2</v>
+        <v>1.98704227385191E-3</v>
+      </c>
+      <c r="D27">
+        <v>2.6292036075572802E-3</v>
       </c>
       <c r="E27">
-        <v>9.7129150493604197E-2</v>
+        <v>1.28502515607631E-3</v>
       </c>
       <c r="F27">
-        <v>0.162339382680384</v>
+        <v>2.9546005186958501E-3</v>
       </c>
       <c r="G27">
-        <v>0.30844867656865799</v>
-      </c>
-      <c r="H27" s="1">
-        <v>0.111594128658959</v>
+        <v>5.1015462550860801E-3</v>
+      </c>
+      <c r="H27">
+        <v>9.6755824484394404E-4</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="B28">
-        <v>-1.48906419380108</v>
+        <v>-2.81704952718385E-2</v>
       </c>
       <c r="C28">
-        <v>-0.75889851269989494</v>
-      </c>
-      <c r="D28" s="1">
-        <v>-0.540199751753348</v>
+        <v>-1.80624658509159E-2</v>
+      </c>
+      <c r="D28">
+        <v>-1.3441391126268101E-2</v>
       </c>
       <c r="E28">
-        <v>-0.52658153640438499</v>
+        <v>-9.6787892248414303E-3</v>
       </c>
       <c r="F28">
-        <v>-0.31440877338108802</v>
+        <v>-8.2658946719153005E-3</v>
       </c>
       <c r="G28">
-        <v>0.57336331839389998</v>
-      </c>
-      <c r="H28" s="1">
-        <v>0.44448973931880698</v>
+        <v>0.33835024044667</v>
+      </c>
+      <c r="H28">
+        <v>9.7965711790006203E-3</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="B29">
-        <v>-1.4920496314473599</v>
+        <v>-5.4002372350003602E-2</v>
       </c>
       <c r="C29">
-        <v>-0.76217735772487205</v>
-      </c>
-      <c r="D29" s="1">
-        <v>-0.541915196681379</v>
+        <v>1.3279899597224401E-3</v>
+      </c>
+      <c r="D29">
+        <v>2.0231503021879101E-3</v>
       </c>
       <c r="E29">
-        <v>-0.52896539076896198</v>
+        <v>1.6719977622898399E-3</v>
       </c>
       <c r="F29">
-        <v>-0.31620613308212397</v>
+        <v>2.58283333814585E-3</v>
       </c>
       <c r="G29">
-        <v>0.59059396563195599</v>
-      </c>
-      <c r="H29" s="1">
-        <v>0.44597122464274802</v>
+        <v>4.2766152783315602E-3</v>
+      </c>
+      <c r="H29">
+        <v>1.2548433784234101E-3</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="B30">
-        <v>-0.46702043761506801</v>
+        <v>-2.2742259454224801E-2</v>
       </c>
       <c r="C30">
-        <v>4.8353885136052703E-2</v>
-      </c>
-      <c r="D30" s="1">
-        <v>8.1670778144648098E-2</v>
+        <v>-1.42074756169336E-2</v>
+      </c>
+      <c r="D30">
+        <v>-1.04625163583172E-2</v>
       </c>
       <c r="E30">
-        <v>9.4666192141727404E-2</v>
+        <v>-7.22638415887815E-3</v>
       </c>
       <c r="F30">
-        <v>0.15872261393727799</v>
+        <v>-6.2503376881629102E-3</v>
       </c>
       <c r="G30">
-        <v>0.30361263445976999</v>
-      </c>
-      <c r="H30" s="1">
-        <v>0.110368728801225</v>
+        <v>0.30776312874047002</v>
+      </c>
+      <c r="H30">
+        <v>7.9571379287706693E-3</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="B31">
-        <v>-1.1441164726733199E-5</v>
+        <v>-0.25293638742417701</v>
       </c>
       <c r="C31">
-        <v>0</v>
-      </c>
-      <c r="D31" s="1">
-        <v>3.8232031975837799E-6</v>
+        <v>4.0454303692551499E-2</v>
+      </c>
+      <c r="D31">
+        <v>7.2726369786816999E-2</v>
       </c>
       <c r="E31">
-        <v>1.1900803639816101E-5</v>
+        <v>8.9781080028362006E-2</v>
       </c>
       <c r="F31">
-        <v>1.14427229127578E-5</v>
+        <v>0.14833225012444501</v>
       </c>
       <c r="G31">
-        <v>3.7957322504667001E-4</v>
-      </c>
-      <c r="H31" s="1">
-        <v>1.14427229127578E-5</v>
+        <v>0.283769259002909</v>
+      </c>
+      <c r="H31">
+        <v>0.107877946431893</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B32">
-        <v>-0.55216979913414999</v>
+        <v>-0.25274767612922699</v>
       </c>
       <c r="C32">
-        <v>5.5699572767002103E-2</v>
-      </c>
-      <c r="D32" s="1">
-        <v>9.0212819583777498E-2</v>
+        <v>3.9928052598467302E-2</v>
+      </c>
+      <c r="D32">
+        <v>7.1898287867641505E-2</v>
       </c>
       <c r="E32">
-        <v>0.102272735264575</v>
+        <v>8.9104726559884606E-2</v>
       </c>
       <c r="F32">
-        <v>0.16988824543981401</v>
+        <v>0.14748194601008699</v>
       </c>
       <c r="G32">
-        <v>0.31788062985976201</v>
-      </c>
-      <c r="H32" s="1">
-        <v>0.11418867267281201</v>
+        <v>0.28278134028027102</v>
+      </c>
+      <c r="H32">
+        <v>0.10755389341162</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1" xr:uid="{00000000-0001-0000-0200-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H32">
-      <sortCondition ref="A1"/>
-    </sortState>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -3064,16 +3043,16 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>335</v>
+        <v>362</v>
       </c>
       <c r="C2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>15.952380952381001</v>
+        <v>15.0833333333333</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -3081,16 +3060,16 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>335</v>
+        <v>364</v>
       </c>
       <c r="C3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>15.952380952381001</v>
+        <v>16.545454545454501</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -3098,7 +3077,7 @@
         <v>10</v>
       </c>
       <c r="B4">
-        <v>335</v>
+        <v>365</v>
       </c>
       <c r="C4">
         <v>21</v>
@@ -3107,7 +3086,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>15.952380952381001</v>
+        <v>17.380952380952401</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -3115,16 +3094,16 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5">
-        <v>334</v>
+        <v>363</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>6.5868263473053898E-2</v>
+        <v>6.3360881542699699E-2</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -3132,16 +3111,16 @@
         <v>12</v>
       </c>
       <c r="B6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6">
-        <v>334</v>
+        <v>363</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>6.5868263473053898E-2</v>
+        <v>6.3360881542699699E-2</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -3149,16 +3128,16 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>334</v>
+        <v>363</v>
       </c>
       <c r="C7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>15.181818181818199</v>
+        <v>15.7826086956522</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -3166,16 +3145,16 @@
         <v>14</v>
       </c>
       <c r="B8">
-        <v>334</v>
+        <v>363</v>
       </c>
       <c r="C8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>15.181818181818199</v>
+        <v>15.7826086956522</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -3183,16 +3162,16 @@
         <v>15</v>
       </c>
       <c r="B9">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="C9">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D9">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E9">
-        <v>4.6481481481481497</v>
+        <v>4.7586206896551699</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -3200,16 +3179,16 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>334</v>
+        <v>363</v>
       </c>
       <c r="C10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10">
-        <v>15.181818181818199</v>
+        <v>15.7826086956522</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -3217,16 +3196,16 @@
         <v>17</v>
       </c>
       <c r="B11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11">
-        <v>334</v>
+        <v>363</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>6.5868263473053898E-2</v>
+        <v>6.3360881542699699E-2</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -3234,16 +3213,16 @@
         <v>18</v>
       </c>
       <c r="B12">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C12">
-        <v>334</v>
+        <v>363</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>6.5868263473053898E-2</v>
+        <v>6.3360881542699699E-2</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -3251,16 +3230,16 @@
         <v>19</v>
       </c>
       <c r="B13">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13">
-        <v>335</v>
+        <v>364</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>6.2686567164179099E-2</v>
+        <v>6.0439560439560398E-2</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -3271,13 +3250,13 @@
         <v>21</v>
       </c>
       <c r="C14">
-        <v>335</v>
+        <v>365</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>6.2686567164179099E-2</v>
+        <v>5.75342465753425E-2</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
@@ -3285,16 +3264,16 @@
         <v>21</v>
       </c>
       <c r="B15">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C15">
-        <v>334</v>
+        <v>363</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>6.5868263473053898E-2</v>
+        <v>6.3360881542699699E-2</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -3302,16 +3281,16 @@
         <v>22</v>
       </c>
       <c r="B16">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16">
-        <v>334</v>
+        <v>363</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>6.5868263473053898E-2</v>
+        <v>6.3360881542699699E-2</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
@@ -3319,16 +3298,16 @@
         <v>23</v>
       </c>
       <c r="B17">
-        <v>334</v>
+        <v>363</v>
       </c>
       <c r="C17">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>15.181818181818199</v>
+        <v>15.7826086956522</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -3336,16 +3315,16 @@
         <v>24</v>
       </c>
       <c r="B18">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18">
-        <v>334</v>
+        <v>363</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>6.5868263473053898E-2</v>
+        <v>6.3360881542699699E-2</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -3353,16 +3332,16 @@
         <v>25</v>
       </c>
       <c r="B19">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C19">
-        <v>334</v>
+        <v>363</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>6.5868263473053898E-2</v>
+        <v>6.3360881542699699E-2</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
@@ -3370,16 +3349,16 @@
         <v>26</v>
       </c>
       <c r="B20">
-        <v>334</v>
+        <v>363</v>
       </c>
       <c r="C20">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>15.181818181818199</v>
+        <v>15.7826086956522</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
@@ -3387,16 +3366,16 @@
         <v>27</v>
       </c>
       <c r="B21">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C21">
-        <v>334</v>
+        <v>363</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>6.5868263473053898E-2</v>
+        <v>6.3360881542699699E-2</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
@@ -3404,16 +3383,16 @@
         <v>28</v>
       </c>
       <c r="B22">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C22">
-        <v>340</v>
+        <v>369</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
-        <v>4.7058823529411799E-2</v>
+        <v>4.6070460704606998E-2</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
@@ -3421,16 +3400,16 @@
         <v>29</v>
       </c>
       <c r="B23">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C23">
-        <v>334</v>
+        <v>363</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23">
-        <v>6.5868263473053898E-2</v>
+        <v>6.3360881542699699E-2</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
@@ -3438,16 +3417,16 @@
         <v>30</v>
       </c>
       <c r="B24">
-        <v>334</v>
+        <v>363</v>
       </c>
       <c r="C24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24">
-        <v>15.181818181818199</v>
+        <v>15.7826086956522</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
@@ -3455,16 +3434,16 @@
         <v>31</v>
       </c>
       <c r="B25">
-        <v>334</v>
+        <v>363</v>
       </c>
       <c r="C25">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25">
-        <v>15.181818181818199</v>
+        <v>15.7826086956522</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
@@ -3472,16 +3451,16 @@
         <v>32</v>
       </c>
       <c r="B26">
-        <v>335</v>
+        <v>362</v>
       </c>
       <c r="C26">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
       <c r="E26">
-        <v>15.952380952381001</v>
+        <v>15.0833333333333</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
@@ -3489,16 +3468,16 @@
         <v>33</v>
       </c>
       <c r="B27">
-        <v>334</v>
+        <v>363</v>
       </c>
       <c r="C27">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27">
-        <v>15.181818181818199</v>
+        <v>15.7826086956522</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
@@ -3506,16 +3485,16 @@
         <v>34</v>
       </c>
       <c r="B28">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C28">
-        <v>334</v>
+        <v>363</v>
       </c>
       <c r="D28">
         <v>0</v>
       </c>
       <c r="E28">
-        <v>6.5868263473053898E-2</v>
+        <v>6.3360881542699699E-2</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
@@ -3523,16 +3502,16 @@
         <v>35</v>
       </c>
       <c r="B29">
-        <v>335</v>
+        <v>364</v>
       </c>
       <c r="C29">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29">
-        <v>15.952380952381001</v>
+        <v>16.545454545454501</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
@@ -3540,16 +3519,16 @@
         <v>36</v>
       </c>
       <c r="B30">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C30">
-        <v>334</v>
+        <v>363</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30">
-        <v>6.5868263473053898E-2</v>
+        <v>6.3360881542699699E-2</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
@@ -3557,16 +3536,16 @@
         <v>37</v>
       </c>
       <c r="B31">
-        <v>335</v>
+        <v>362</v>
       </c>
       <c r="C31">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D31">
         <v>0</v>
       </c>
       <c r="E31">
-        <v>15.952380952381001</v>
+        <v>15.0833333333333</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
@@ -3574,20 +3553,26 @@
         <v>38</v>
       </c>
       <c r="B32">
-        <v>335</v>
+        <v>362</v>
       </c>
       <c r="C32">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>15.952380952381001</v>
+        <v>15.0833333333333</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{db3dbd43-4c4b-4544-9f8a-0553f9f5f25e}" enabled="0" method="" siteId="{db3dbd43-4c4b-4544-9f8a-0553f9f5f25e}" removed="1"/>
+</clbl:labelList>
 </file>
--- a/Zinc/7. Sensitivity analyses/Plots of DIC SA/Carbonate_system_SA.xlsx
+++ b/Zinc/7. Sensitivity analyses/Plots of DIC SA/Carbonate_system_SA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ornl-my.sharepoint.com/personal/q4q_ornl_gov/Documents/Research/Bioavailability Project/BLM_spatial_assessmt/Zinc/7. Sensitivity analyses/Plots of DIC SA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_27F50F9DD8F835CF593FF6452A392FE477740235" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA220FE6-512E-4D25-9E70-4B70BFA5999D}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_27F50F9DD8F835CF593FF6452A392FE477740235" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D47007CF-D84E-4A54-B224-D70C8B66794A}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="19200" windowHeight="11280" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Delta" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,9 @@
     <sheet name="Log Response Ratio" sheetId="3" r:id="rId3"/>
     <sheet name="Robustness" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Percent Change'!$A$1:$H$1</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -205,6 +208,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1363,811 +1370,816 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B2">
-        <v>-1538.1072415721001</v>
+        <v>-422718221.67094803</v>
       </c>
       <c r="C2">
-        <v>111.77736514155799</v>
-      </c>
-      <c r="D2">
-        <v>427.38697025867998</v>
+        <v>-249316661.21119601</v>
+      </c>
+      <c r="D2" s="1">
+        <v>-187279001.69324201</v>
       </c>
       <c r="E2">
-        <v>765.57775061146594</v>
+        <v>-151854309.88492301</v>
       </c>
       <c r="F2">
-        <v>1047.56976426756</v>
+        <v>-112898482.98474699</v>
       </c>
       <c r="G2">
-        <v>8049.6988630329697</v>
+        <v>2423397568.0545001</v>
       </c>
       <c r="H2">
-        <v>935.79239912600497</v>
+        <v>136418178.22644901</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B3">
-        <v>-549.29940596082395</v>
+        <v>-131301469.80984101</v>
       </c>
       <c r="C3">
-        <v>2.57953068627529</v>
-      </c>
-      <c r="D3">
-        <v>7.70880269340695</v>
+        <v>-19773908.5706416</v>
+      </c>
+      <c r="D3" s="1">
+        <v>-9584200.0519041903</v>
       </c>
       <c r="E3">
-        <v>4.6524934654724603</v>
+        <v>-16467349.499102499</v>
       </c>
       <c r="F3">
-        <v>15.555863194793901</v>
+        <v>-4247814.6042412901</v>
       </c>
       <c r="G3">
-        <v>83.585205423730997</v>
+        <v>2408482.8737613899</v>
       </c>
       <c r="H3">
-        <v>12.976332508518601</v>
+        <v>15526093.966400299</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="B4">
-        <v>-8570.4300545331098</v>
+        <v>-6114613.0747147296</v>
       </c>
       <c r="C4">
-        <v>0.316190053740315</v>
-      </c>
-      <c r="D4">
-        <v>1.38660610771168</v>
+        <v>-2679989.9160323502</v>
+      </c>
+      <c r="D4" s="1">
+        <v>-1787304.15427708</v>
       </c>
       <c r="E4">
-        <v>-56.435077171495003</v>
+        <v>-1706921.0758665199</v>
       </c>
       <c r="F4">
-        <v>4.0703850012757297</v>
+        <v>-720660.96095113596</v>
       </c>
       <c r="G4">
-        <v>101.09513226553</v>
+        <v>8209638.6904595597</v>
       </c>
       <c r="H4">
-        <v>3.7541949475354199</v>
+        <v>1959328.95508122</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B5">
-        <v>-1580.2621433636</v>
+        <v>-2413800.3254847699</v>
       </c>
       <c r="C5">
-        <v>-333.595440160652</v>
-      </c>
-      <c r="D5">
-        <v>-183.906102846354</v>
+        <v>-959914.64377220999</v>
+      </c>
+      <c r="D5" s="1">
+        <v>-635876.06149440003</v>
       </c>
       <c r="E5">
-        <v>-68.323727767007696</v>
+        <v>-617966.49983508</v>
       </c>
       <c r="F5">
-        <v>-81.159449646928095</v>
+        <v>-301512.08818551898</v>
       </c>
       <c r="G5">
-        <v>13089.374917285601</v>
+        <v>4208029.0768353697</v>
       </c>
       <c r="H5">
-        <v>252.43599051372399</v>
+        <v>658402.55558669101</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B6">
-        <v>-10922.9246092468</v>
+        <v>-1896907.4517372099</v>
       </c>
       <c r="C6">
-        <v>-2179.7856519789598</v>
-      </c>
-      <c r="D6">
-        <v>-1380.1536802304799</v>
+        <v>-527854.22681722604</v>
+      </c>
+      <c r="D6" s="1">
+        <v>-278278.75612729299</v>
       </c>
       <c r="E6">
-        <v>-1521.5318678641299</v>
+        <v>264114.58349585498</v>
       </c>
       <c r="F6">
-        <v>-481.52545284452299</v>
+        <v>-108853.31889198899</v>
       </c>
       <c r="G6">
-        <v>2917.4913152019199</v>
+        <v>60701825.714204498</v>
       </c>
       <c r="H6">
-        <v>1698.26019913444</v>
+        <v>419000.90792523802</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B7">
-        <v>-57.1250935443854</v>
+        <v>-328223.45019667398</v>
       </c>
       <c r="C7">
-        <v>1.6828528154322799</v>
-      </c>
-      <c r="D7">
-        <v>5.3050591697356202</v>
+        <v>-119601.88714965701</v>
+      </c>
+      <c r="D7" s="1">
+        <v>-64893.179008151899</v>
       </c>
       <c r="E7">
-        <v>7.3585170515330498</v>
+        <v>115190.337245332</v>
       </c>
       <c r="F7">
-        <v>11.136628425001399</v>
+        <v>-22153.694545501501</v>
       </c>
       <c r="G7">
-        <v>69.407146696675994</v>
+        <v>20992555.073462401</v>
       </c>
       <c r="H7">
-        <v>9.4537756095691208</v>
+        <v>97448.192604155498</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B8">
-        <v>-2.3132318976992798</v>
+        <v>-377670.22932951699</v>
       </c>
       <c r="C8">
-        <v>4.0348903688688702E-2</v>
+        <v>-28115.042353802601</v>
       </c>
       <c r="D8">
-        <v>0.21919844411799699</v>
+        <v>-12317.803306223601</v>
       </c>
       <c r="E8">
-        <v>0.51132910854023295</v>
+        <v>-25307.878882808702</v>
       </c>
       <c r="F8">
-        <v>0.61840372232724194</v>
+        <v>-4744.4685546016899</v>
       </c>
       <c r="G8">
-        <v>15.8968435637341</v>
+        <v>120682.438633709</v>
       </c>
       <c r="H8">
-        <v>0.57805481863855401</v>
+        <v>23370.573799200902</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="B9">
-        <v>-2.6337430704085401E-10</v>
+        <v>-49494.423254303998</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>-4718.1365007653803</v>
       </c>
       <c r="D9">
-        <v>8.8012017179612599E-11</v>
+        <v>-2211.2455736255001</v>
       </c>
       <c r="E9">
-        <v>3.5525907240701298E-10</v>
+        <v>-3622.02563760765</v>
       </c>
       <c r="F9">
-        <v>3.0771118786972598E-10</v>
+        <v>-1001.8572898370001</v>
       </c>
       <c r="G9">
-        <v>8.6595883967004301E-9</v>
+        <v>20322.932531290298</v>
       </c>
       <c r="H9">
-        <v>3.0771118786972598E-10</v>
+        <v>3716.2792109283801</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B10">
-        <v>-9758.1557759256993</v>
+        <v>-10922.9246092468</v>
       </c>
       <c r="C10">
-        <v>389.18220209588998</v>
+        <v>-2179.7856519789598</v>
       </c>
       <c r="D10">
-        <v>851.44053293994</v>
+        <v>-1380.1536802304799</v>
       </c>
       <c r="E10">
-        <v>868.17506098497802</v>
+        <v>-1521.5318678641299</v>
       </c>
       <c r="F10">
-        <v>1355.5780266773099</v>
+        <v>-481.52545284452299</v>
       </c>
       <c r="G10">
-        <v>5136.6511162331999</v>
+        <v>2917.4913152019199</v>
       </c>
       <c r="H10">
-        <v>966.39582458142002</v>
+        <v>1698.26019913444</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B11">
-        <v>-422718221.67094803</v>
+        <v>-10226.4804291401</v>
       </c>
       <c r="C11">
-        <v>-249316661.21119601</v>
+        <v>-1957.19118759001</v>
       </c>
       <c r="D11">
-        <v>-187279001.69324201</v>
+        <v>-1024.6726018899101</v>
       </c>
       <c r="E11">
-        <v>-151854309.88492301</v>
+        <v>-969.58137171118597</v>
       </c>
       <c r="F11">
-        <v>-112898482.98474699</v>
+        <v>-568.58759229122597</v>
       </c>
       <c r="G11">
-        <v>2423397568.0545001</v>
+        <v>50090.705827621001</v>
       </c>
       <c r="H11">
-        <v>136418178.22644901</v>
+        <v>1388.60359529879</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B12">
-        <v>-131301469.80984101</v>
+        <v>-1580.2621433636</v>
       </c>
       <c r="C12">
-        <v>-19773908.5706416</v>
+        <v>-333.595440160652</v>
       </c>
       <c r="D12">
-        <v>-9584200.0519041903</v>
+        <v>-183.906102846354</v>
       </c>
       <c r="E12">
-        <v>-16467349.499102499</v>
+        <v>-68.323727767007696</v>
       </c>
       <c r="F12">
-        <v>-4247814.6042412901</v>
+        <v>-81.159449646928095</v>
       </c>
       <c r="G12">
-        <v>2408482.8737613899</v>
+        <v>13089.374917285601</v>
       </c>
       <c r="H12">
-        <v>15526093.966400299</v>
+        <v>252.43599051372399</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="B13">
-        <v>-7.0924223479098003E-9</v>
+        <v>-9.6695681519959997E-2</v>
       </c>
       <c r="C13">
-        <v>-2.79779978438966E-10</v>
+        <v>-2.3567226731304899E-2</v>
       </c>
       <c r="D13">
-        <v>-1.4165835536043601E-10</v>
+        <v>-1.40690270800074E-2</v>
       </c>
       <c r="E13">
-        <v>-2.5880822096539002E-10</v>
+        <v>1.9695437796516798E-3</v>
       </c>
       <c r="F13">
-        <v>-5.7013565084091202E-11</v>
+        <v>-6.4800827059847497E-3</v>
       </c>
       <c r="G13">
-        <v>1.15165594031759E-10</v>
+        <v>2.4218736664283398</v>
       </c>
       <c r="H13">
-        <v>2.2276641335487399E-10</v>
+        <v>1.7087144025320199E-2</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B14">
-        <v>-6.6761954034308002E-9</v>
+        <v>-0.17941493697866001</v>
       </c>
       <c r="C14">
-        <v>-1.0559887209922E-10</v>
+        <v>-2.9084871528647301E-2</v>
       </c>
       <c r="D14">
-        <v>-2.65132590904378E-11</v>
+        <v>-1.3740523228799499E-2</v>
       </c>
       <c r="E14">
-        <v>-1.7201849080841399E-10</v>
+        <v>-2.09181248637458E-2</v>
       </c>
       <c r="F14">
-        <v>-7.2553847237906499E-12</v>
+        <v>-6.9365472359352396E-3</v>
       </c>
       <c r="G14">
-        <v>6.1117661275200297E-12</v>
+        <v>1.2524722804679899E-2</v>
       </c>
       <c r="H14">
-        <v>9.8343487375429295E-11</v>
+        <v>2.2148324292712102E-2</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B15">
-        <v>-2413800.3254847699</v>
+        <v>-7.0924223479098003E-9</v>
       </c>
       <c r="C15">
-        <v>-959914.64377220999</v>
+        <v>-2.79779978438966E-10</v>
       </c>
       <c r="D15">
-        <v>-635876.06149440003</v>
+        <v>-1.4165835536043601E-10</v>
       </c>
       <c r="E15">
-        <v>-617966.49983508</v>
+        <v>-2.5880822096539002E-10</v>
       </c>
       <c r="F15">
-        <v>-301512.08818551898</v>
+        <v>-5.7013565084091202E-11</v>
       </c>
       <c r="G15">
-        <v>4208029.0768353697</v>
+        <v>1.15165594031759E-10</v>
       </c>
       <c r="H15">
-        <v>658402.55558669101</v>
+        <v>2.2276641335487399E-10</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B16">
-        <v>-328223.45019667398</v>
+        <v>-6.6761954034308002E-9</v>
       </c>
       <c r="C16">
-        <v>-119601.88714965701</v>
+        <v>-1.0559887209922E-10</v>
       </c>
       <c r="D16">
-        <v>-64893.179008151899</v>
+        <v>-2.65132590904378E-11</v>
       </c>
       <c r="E16">
-        <v>115190.337245332</v>
+        <v>-1.7201849080841399E-10</v>
       </c>
       <c r="F16">
-        <v>-22153.694545501501</v>
+        <v>-7.2553847237906499E-12</v>
       </c>
       <c r="G16">
-        <v>20992555.073462401</v>
+        <v>6.1117661275200297E-12</v>
       </c>
       <c r="H16">
-        <v>97448.192604155498</v>
+        <v>9.8343487375429295E-11</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B17">
-        <v>-960822.21716641996</v>
+        <v>-2.6337430704085401E-10</v>
       </c>
       <c r="C17">
-        <v>7496.8653507312201</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>16875.264918780998</v>
+        <v>8.8012017179612599E-11</v>
       </c>
       <c r="E17">
-        <v>12650.7173616408</v>
+        <v>3.5525907240701298E-10</v>
       </c>
       <c r="F17">
-        <v>29213.7087853915</v>
+        <v>3.0771118786972598E-10</v>
       </c>
       <c r="G17">
-        <v>128618.55793744</v>
+        <v>8.6595883967004301E-9</v>
       </c>
       <c r="H17">
-        <v>21716.843434660299</v>
+        <v>3.0771118786972598E-10</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="B18">
-        <v>-6114613.0747147296</v>
+        <v>-0.16630544948169099</v>
       </c>
       <c r="C18">
-        <v>-2679989.9160323502</v>
+        <v>1.25750804166048E-3</v>
       </c>
       <c r="D18">
-        <v>-1787304.15427708</v>
+        <v>3.2041883374801798E-3</v>
       </c>
       <c r="E18">
-        <v>-1706921.0758665199</v>
+        <v>2.6618285314725198E-3</v>
       </c>
       <c r="F18">
-        <v>-720660.96095113596</v>
+        <v>6.3173473067235199E-3</v>
       </c>
       <c r="G18">
-        <v>8209638.6904595597</v>
+        <v>2.9198909318277001E-2</v>
       </c>
       <c r="H18">
-        <v>1959328.95508122</v>
+        <v>5.0598392650630496E-3</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B19">
-        <v>-1896907.4517372099</v>
+        <v>-1.6615631677728501E-2</v>
       </c>
       <c r="C19">
-        <v>-527854.22681722604</v>
+        <v>1.4882820110672899E-3</v>
       </c>
       <c r="D19">
-        <v>-278278.75612729299</v>
+        <v>5.0759174528211002E-3</v>
       </c>
       <c r="E19">
-        <v>264114.58349585498</v>
+        <v>9.4630754540868198E-3</v>
       </c>
       <c r="F19">
-        <v>-108853.31889198899</v>
+        <v>1.2179799604918501E-2</v>
       </c>
       <c r="G19">
-        <v>60701825.714204498</v>
+        <v>9.2757985648146996E-2</v>
       </c>
       <c r="H19">
-        <v>419000.90792523802</v>
+        <v>1.0691517593851301E-2</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="B20">
-        <v>-2655196.6584520498</v>
+        <v>-0.17456829613396899</v>
       </c>
       <c r="C20">
-        <v>19726.4398593687</v>
-      </c>
-      <c r="D20">
-        <v>43255.658965787603</v>
+        <v>3.38077469622208E-3</v>
+      </c>
+      <c r="D20" s="1">
+        <v>8.8386555109915502E-3</v>
       </c>
       <c r="E20">
-        <v>38551.666220896899</v>
+        <v>1.21249039855593E-2</v>
       </c>
       <c r="F20">
-        <v>93272.888079804994</v>
+        <v>1.8358907505559598E-2</v>
       </c>
       <c r="G20">
-        <v>270006.78528565902</v>
+        <v>0.10631107883518701</v>
       </c>
       <c r="H20">
-        <v>73546.448220436301</v>
+        <v>1.49781328093375E-2</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B21">
-        <v>-377670.22932951699</v>
+        <v>-0.59582971146590002</v>
       </c>
       <c r="C21">
-        <v>-28115.042353802601</v>
+        <v>1.1985228712229999E-2</v>
       </c>
       <c r="D21">
-        <v>-12317.803306223601</v>
+        <v>1.8918221547869998E-2</v>
       </c>
       <c r="E21">
-        <v>-25307.878882808702</v>
+        <v>1.84616772291127E-2</v>
       </c>
       <c r="F21">
-        <v>-4744.4685546016899</v>
+        <v>2.8165491810632801E-2</v>
       </c>
       <c r="G21">
-        <v>120682.438633709</v>
+        <v>8.0481365346869699E-2</v>
       </c>
       <c r="H21">
-        <v>23370.573799200902</v>
+        <v>1.61802630984028E-2</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="B22">
-        <v>-49494.423254303998</v>
+        <v>-2.3132318976992798</v>
       </c>
       <c r="C22">
-        <v>-4718.1365007653803</v>
+        <v>4.0348903688688702E-2</v>
       </c>
       <c r="D22">
-        <v>-2211.2455736255001</v>
+        <v>0.21919844411799699</v>
       </c>
       <c r="E22">
-        <v>-3622.02563760765</v>
+        <v>0.51132910854023295</v>
       </c>
       <c r="F22">
-        <v>-1001.8572898370001</v>
+        <v>0.61840372232724194</v>
       </c>
       <c r="G22">
-        <v>20322.932531290298</v>
+        <v>15.8968435637341</v>
       </c>
       <c r="H22">
-        <v>3716.2792109283801</v>
+        <v>0.57805481863855401</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B23">
-        <v>-10226.4804291401</v>
+        <v>-10.902772888114701</v>
       </c>
       <c r="C23">
-        <v>-1957.19118759001</v>
+        <v>0.16802733201244899</v>
       </c>
       <c r="D23">
-        <v>-1024.6726018899101</v>
+        <v>0.233206263228</v>
       </c>
       <c r="E23">
-        <v>-969.58137171118597</v>
+        <v>0.125253556633626</v>
       </c>
       <c r="F23">
-        <v>-568.58759229122597</v>
+        <v>0.26897538416945099</v>
       </c>
       <c r="G23">
-        <v>50090.705827621001</v>
+        <v>0.37610096893310202</v>
       </c>
       <c r="H23">
-        <v>1388.60359529879</v>
+        <v>0.10094805215700201</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="B24">
-        <v>-27077.112463310001</v>
+        <v>-8570.4300545331098</v>
       </c>
       <c r="C24">
-        <v>894.395313366653</v>
+        <v>0.316190053740315</v>
       </c>
       <c r="D24">
-        <v>2302.8228213206498</v>
+        <v>1.38660610771168</v>
       </c>
       <c r="E24">
-        <v>4140.0817677973901</v>
+        <v>-56.435077171495003</v>
       </c>
       <c r="F24">
-        <v>5537.6318641719799</v>
+        <v>4.0703850012757297</v>
       </c>
       <c r="G24">
-        <v>88074.1936271101</v>
+        <v>101.09513226553</v>
       </c>
       <c r="H24">
-        <v>4643.2365508053199</v>
+        <v>3.7541949475354199</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="B25">
-        <v>-24933.6949309505</v>
+        <v>-57.1250935443854</v>
       </c>
       <c r="C25">
-        <v>155.359902720419</v>
+        <v>1.6828528154322799</v>
       </c>
       <c r="D25">
-        <v>379.43337360957503</v>
+        <v>5.3050591697356202</v>
       </c>
       <c r="E25">
-        <v>818.11363325768502</v>
+        <v>7.3585170515330498</v>
       </c>
       <c r="F25">
-        <v>1085.5487175831699</v>
+        <v>11.136628425001399</v>
       </c>
       <c r="G25">
-        <v>20174.297787889001</v>
+        <v>69.407146696675994</v>
       </c>
       <c r="H25">
-        <v>930.18881486275495</v>
+        <v>9.4537756095691208</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="B26">
-        <v>-1.6615631677728501E-2</v>
+        <v>-549.29940596082395</v>
       </c>
       <c r="C26">
-        <v>1.4882820110672899E-3</v>
+        <v>2.57953068627529</v>
       </c>
       <c r="D26">
-        <v>5.0759174528211002E-3</v>
+        <v>7.70880269340695</v>
       </c>
       <c r="E26">
-        <v>9.4630754540868198E-3</v>
+        <v>4.6524934654724603</v>
       </c>
       <c r="F26">
-        <v>1.2179799604918501E-2</v>
+        <v>15.555863194793901</v>
       </c>
       <c r="G26">
-        <v>9.2757985648146996E-2</v>
+        <v>83.585205423730997</v>
       </c>
       <c r="H26">
-        <v>1.0691517593851301E-2</v>
+        <v>12.976332508518601</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B27">
-        <v>-10.902772888114701</v>
+        <v>-24933.6949309505</v>
       </c>
       <c r="C27">
-        <v>0.16802733201244899</v>
+        <v>155.359902720419</v>
       </c>
       <c r="D27">
-        <v>0.233206263228</v>
+        <v>379.43337360957503</v>
       </c>
       <c r="E27">
-        <v>0.125253556633626</v>
+        <v>818.11363325768502</v>
       </c>
       <c r="F27">
-        <v>0.26897538416945099</v>
+        <v>1085.5487175831699</v>
       </c>
       <c r="G27">
-        <v>0.37610096893310202</v>
+        <v>20174.297787889001</v>
       </c>
       <c r="H27">
-        <v>0.10094805215700201</v>
+        <v>930.18881486275495</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="B28">
-        <v>-0.17941493697866001</v>
+        <v>-1538.1072415721001</v>
       </c>
       <c r="C28">
-        <v>-2.9084871528647301E-2</v>
+        <v>111.77736514155799</v>
       </c>
       <c r="D28">
-        <v>-1.3740523228799499E-2</v>
+        <v>427.38697025867998</v>
       </c>
       <c r="E28">
-        <v>-2.09181248637458E-2</v>
+        <v>765.57775061146594</v>
       </c>
       <c r="F28">
-        <v>-6.9365472359352396E-3</v>
+        <v>1047.56976426756</v>
       </c>
       <c r="G28">
-        <v>1.2524722804679899E-2</v>
+        <v>8049.6988630329697</v>
       </c>
       <c r="H28">
-        <v>2.2148324292712102E-2</v>
+        <v>935.79239912600497</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="B29">
-        <v>-0.59582971146590002</v>
+        <v>-9758.1557759256993</v>
       </c>
       <c r="C29">
-        <v>1.1985228712229999E-2</v>
+        <v>389.18220209588998</v>
       </c>
       <c r="D29">
-        <v>1.8918221547869998E-2</v>
+        <v>851.44053293994</v>
       </c>
       <c r="E29">
-        <v>1.84616772291127E-2</v>
+        <v>868.17506098497802</v>
       </c>
       <c r="F29">
-        <v>2.8165491810632801E-2</v>
+        <v>1355.5780266773099</v>
       </c>
       <c r="G29">
-        <v>8.0481365346869699E-2</v>
+        <v>5136.6511162331999</v>
       </c>
       <c r="H29">
-        <v>1.61802630984028E-2</v>
+        <v>966.39582458142002</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B30">
-        <v>-9.6695681519959997E-2</v>
+        <v>-27077.112463310001</v>
       </c>
       <c r="C30">
-        <v>-2.3567226731304899E-2</v>
+        <v>894.395313366653</v>
       </c>
       <c r="D30">
-        <v>-1.40690270800074E-2</v>
+        <v>2302.8228213206498</v>
       </c>
       <c r="E30">
-        <v>1.9695437796516798E-3</v>
+        <v>4140.0817677973901</v>
       </c>
       <c r="F30">
-        <v>-6.4800827059847497E-3</v>
+        <v>5537.6318641719799</v>
       </c>
       <c r="G30">
-        <v>2.4218736664283398</v>
+        <v>88074.1936271101</v>
       </c>
       <c r="H30">
-        <v>1.7087144025320199E-2</v>
+        <v>4643.2365508053199</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="B31">
-        <v>-0.16630544948169099</v>
+        <v>-960822.21716641996</v>
       </c>
       <c r="C31">
-        <v>1.25750804166048E-3</v>
+        <v>7496.8653507312201</v>
       </c>
       <c r="D31">
-        <v>3.2041883374801798E-3</v>
+        <v>16875.264918780998</v>
       </c>
       <c r="E31">
-        <v>2.6618285314725198E-3</v>
+        <v>12650.7173616408</v>
       </c>
       <c r="F31">
-        <v>6.3173473067235199E-3</v>
+        <v>29213.7087853915</v>
       </c>
       <c r="G31">
-        <v>2.9198909318277001E-2</v>
+        <v>128618.55793744</v>
       </c>
       <c r="H31">
-        <v>5.0598392650630496E-3</v>
+        <v>21716.843434660299</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="B32">
-        <v>-0.17456829613396899</v>
+        <v>-2655196.6584520498</v>
       </c>
       <c r="C32">
-        <v>3.38077469622208E-3</v>
-      </c>
-      <c r="D32" s="1">
-        <v>8.8386555109915502E-3</v>
+        <v>19726.4398593687</v>
+      </c>
+      <c r="D32">
+        <v>43255.658965787603</v>
       </c>
       <c r="E32">
-        <v>1.21249039855593E-2</v>
+        <v>38551.666220896899</v>
       </c>
       <c r="F32">
-        <v>1.8358907505559598E-2</v>
+        <v>93272.888079804994</v>
       </c>
       <c r="G32">
-        <v>0.10631107883518701</v>
+        <v>270006.78528565902</v>
       </c>
       <c r="H32">
-        <v>1.49781328093375E-2</v>
+        <v>73546.448220436301</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H1" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H32">
+      <sortCondition ref="D1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
